--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEF742C-B39B-4C48-B9F3-9B8E3BE79CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7171465-21E0-4E0F-B5A6-6D1EC87F8428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="6" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="4" activeTab="6" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome!" sheetId="15" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="842">
   <si>
     <t>Capacitance</t>
   </si>
@@ -2561,6 +2561,30 @@
   </si>
   <si>
     <t>Air Quality Sensor</t>
+  </si>
+  <si>
+    <t>Limit Switch (Thru-Hole)</t>
+  </si>
+  <si>
+    <t>&lt;AliExpress Item&gt;</t>
+  </si>
+  <si>
+    <t>125V</t>
+  </si>
+  <si>
+    <t>https://a.aliexpress.com/_mqu0KvN</t>
+  </si>
+  <si>
+    <t>Limit Switch</t>
+  </si>
+  <si>
+    <t>SPDT Limit Switch Carrier Board</t>
+  </si>
+  <si>
+    <t>Custom part</t>
+  </si>
+  <si>
+    <t>Carrier Board</t>
   </si>
 </sst>
 </file>
@@ -2837,6 +2861,39 @@
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
@@ -2941,23 +2998,6 @@
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
@@ -3028,25 +3068,6 @@
       </extLst>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="1"/>
@@ -3054,10 +3075,13 @@
       </extLst>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -3104,13 +3128,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I50" totalsRowShown="0">
   <autoFilter ref="A1:I50" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="74"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="73"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="66"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="72"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="71"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3122,11 +3146,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:H20" totalsRowShown="0">
   <autoFilter ref="A1:H20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="41"/>
     <tableColumn id="1" xr3:uid="{727DF6C0-6BC9-4CBC-ACBD-F7D7801F3DED}" name="Color"/>
     <tableColumn id="6" xr3:uid="{2F89F121-2031-4E76-8B64-C6BE1AC4E5A7}" name="Mount Type"/>
-    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="40"/>
     <tableColumn id="3" xr3:uid="{95A3DF17-FA71-419C-9869-87ACAC774187}" name="Dome"/>
     <tableColumn id="4" xr3:uid="{30ACC022-FAF3-44FA-97E2-DA5C989B54D7}" name="Part Number"/>
     <tableColumn id="5" xr3:uid="{BDED051F-FA40-461B-85BB-40EDC316E70C}" name="Description"/>
@@ -3136,10 +3160,10 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="39">
   <autoFilter ref="A1:G10" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}"/>
   <tableColumns count="7">
-    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="38"/>
     <tableColumn id="2" xr3:uid="{D4673AC2-9436-437D-9DE0-521034F11263}" name="Memory Organization"/>
     <tableColumn id="6" xr3:uid="{088605FE-5C4A-4A9F-9607-7699E9A0ED47}" name="Total Capacity"/>
     <tableColumn id="7" xr3:uid="{E9CAAB16-100E-4178-A533-7FCE76F08C9F}" name="Interface"/>
@@ -3158,7 +3182,7 @@
     <sortCondition ref="B1:B13"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="37"/>
     <tableColumn id="1" xr3:uid="{07652CF2-D7CA-452D-A87D-CEBA35FEC12A}" name="Function"/>
     <tableColumn id="2" xr3:uid="{A9FCB299-A552-4123-B45A-F31F0DC5BB9B}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{2F50D30B-F60A-4BAF-AE6D-0A3909047904}" name="Description"/>
@@ -3168,17 +3192,17 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="A1:H11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="8">
-    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="75"/>
-    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="72"/>
-    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3305,20 +3329,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="70">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="63"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="69"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="65"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3341,13 +3365,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="61">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="60"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3367,8 +3391,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="58"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3378,11 +3402,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="77">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series" dataDxfId="75"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -3393,25 +3417,25 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="57">
   <autoFilter ref="A1:E11" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="47"/>
-    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="51">
   <autoFilter ref="A1:I10" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="49"/>
     <tableColumn id="4" xr3:uid="{D6AD8AA5-BC88-4F36-A647-B68EB5308316}" name="Automotive Fuse Size"/>
     <tableColumn id="1" xr3:uid="{5D9981C8-F221-4013-A9BA-4E5BF3474E5D}" name="Trip Current"/>
     <tableColumn id="2" xr3:uid="{494ED5E9-E1DA-4E76-9EAF-806837FCC14C}" name="Package"/>
@@ -3425,14 +3449,14 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:E11" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:E11" totalsRowShown="0" headerRowDxfId="48">
   <autoFilter ref="A1:E11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="38"/>
-    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7276,7 +7300,25 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>834</v>
+      </c>
+      <c r="C7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D7" t="s">
+        <v>835</v>
+      </c>
+      <c r="E7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" t="s">
+        <v>836</v>
+      </c>
+      <c r="G7" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -12099,7 +12141,19 @@
     </row>
     <row r="10" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>838</v>
+      </c>
+      <c r="C10" t="s">
+        <v>839</v>
+      </c>
+      <c r="D10" t="s">
+        <v>841</v>
+      </c>
+      <c r="E10" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7171465-21E0-4E0F-B5A6-6D1EC87F8428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5F6B6F-6E3B-4E75-9446-CFB734BE530D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="4" activeTab="6" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="1" activeTab="2" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome!" sheetId="15" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <sheet name="Voltage Regulators" sheetId="4" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Capacitors'!$B$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Capacitors'!$B$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Welcome!'!$A$1:$A$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="872">
   <si>
     <t>Capacitance</t>
   </si>
@@ -91,9 +91,6 @@
     <t>Ceramic</t>
   </si>
   <si>
-    <t>CL10A106KP8NNNC</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -2585,6 +2582,99 @@
   </si>
   <si>
     <t>Carrier Board</t>
+  </si>
+  <si>
+    <t>Standoff</t>
+  </si>
+  <si>
+    <t>Female + Male</t>
+  </si>
+  <si>
+    <t>971050474</t>
+  </si>
+  <si>
+    <t>M4 Nut</t>
+  </si>
+  <si>
+    <t>5mm board-board height</t>
+  </si>
+  <si>
+    <t>Hex Standoff Threaded M4 Brass 0.197" (5.00mm) Silver</t>
+  </si>
+  <si>
+    <t>C0603C120J5GACTU</t>
+  </si>
+  <si>
+    <t>12pF</t>
+  </si>
+  <si>
+    <t>AP63301WU-7</t>
+  </si>
+  <si>
+    <t>Buck Switching Regulator IC Positive Adjustable 0.8V 1 Output 3A SOT-23-6 Thin, TSOT-23-6</t>
+  </si>
+  <si>
+    <t>0-35V</t>
+  </si>
+  <si>
+    <t>0.8-31V</t>
+  </si>
+  <si>
+    <t>SOD-23</t>
+  </si>
+  <si>
+    <t>3.8A</t>
+  </si>
+  <si>
+    <t>SRU1038-100Y</t>
+  </si>
+  <si>
+    <t>10 µH Shielded Drum Core, Wirewound Inductor 3.8 A 25mOhm Nonstandard</t>
+  </si>
+  <si>
+    <t>SMD 10 x 10mm</t>
+  </si>
+  <si>
+    <t>90mA</t>
+  </si>
+  <si>
+    <t>30.1k</t>
+  </si>
+  <si>
+    <t>RC0603FR-0730K1L</t>
+  </si>
+  <si>
+    <t>30.1 kOhms ±1% 0.1W, 1/10W Chip Resistor 0603 (1608 Metric) Moisture Resistant Thick Film</t>
+  </si>
+  <si>
+    <t>422k</t>
+  </si>
+  <si>
+    <t>ERJ-3EKF4223V</t>
+  </si>
+  <si>
+    <t>422 kOhms ±1% 0.1W, 1/10W Chip Resistor 0603 (1608 Metric) Automotive AEC-Q200 Thick Film</t>
+  </si>
+  <si>
+    <t>47pF</t>
+  </si>
+  <si>
+    <t>CL10C470JB8NNNC</t>
+  </si>
+  <si>
+    <t>CGA5L3X5R1H106M160AB</t>
+  </si>
+  <si>
+    <t>Spacer</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/94669A006/</t>
+  </si>
+  <si>
+    <t>Len=4mm, OD=6mm, ID=4mm</t>
+  </si>
+  <si>
+    <t>Aluminum Unthreaded Spacer</t>
   </si>
 </sst>
 </file>
@@ -2723,7 +2813,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="79">
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
@@ -2767,57 +2857,6 @@
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2951,6 +2990,9 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
@@ -2994,6 +3036,23 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <extLst>
@@ -3068,21 +3127,55 @@
       </extLst>
     </dxf>
     <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3125,16 +3218,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I50" totalsRowShown="0">
-  <autoFilter ref="A1:I50" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
+  <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="74"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="68"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="67"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="65"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3146,11 +3239,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:H20" totalsRowShown="0">
   <autoFilter ref="A1:H20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="31"/>
     <tableColumn id="1" xr3:uid="{727DF6C0-6BC9-4CBC-ACBD-F7D7801F3DED}" name="Color"/>
     <tableColumn id="6" xr3:uid="{2F89F121-2031-4E76-8B64-C6BE1AC4E5A7}" name="Mount Type"/>
-    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="30"/>
     <tableColumn id="3" xr3:uid="{95A3DF17-FA71-419C-9869-87ACAC774187}" name="Dome"/>
     <tableColumn id="4" xr3:uid="{30ACC022-FAF3-44FA-97E2-DA5C989B54D7}" name="Part Number"/>
     <tableColumn id="5" xr3:uid="{BDED051F-FA40-461B-85BB-40EDC316E70C}" name="Description"/>
@@ -3160,10 +3253,10 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="29">
   <autoFilter ref="A1:G10" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}"/>
   <tableColumns count="7">
-    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{D4673AC2-9436-437D-9DE0-521034F11263}" name="Memory Organization"/>
     <tableColumn id="6" xr3:uid="{088605FE-5C4A-4A9F-9607-7699E9A0ED47}" name="Total Capacity"/>
     <tableColumn id="7" xr3:uid="{E9CAAB16-100E-4178-A533-7FCE76F08C9F}" name="Interface"/>
@@ -3182,7 +3275,7 @@
     <sortCondition ref="B1:B13"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="27"/>
     <tableColumn id="1" xr3:uid="{07652CF2-D7CA-452D-A87D-CEBA35FEC12A}" name="Function"/>
     <tableColumn id="2" xr3:uid="{A9FCB299-A552-4123-B45A-F31F0DC5BB9B}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{2F50D30B-F60A-4BAF-AE6D-0A3909047904}" name="Description"/>
@@ -3192,54 +3285,54 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="26">
   <autoFilter ref="A1:H11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="8">
-    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="34"/>
-    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}" name="MCUs" displayName="MCUs" ref="A1:J11" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}" name="MCUs" displayName="MCUs" ref="A1:J11" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:J11" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J11">
     <sortCondition ref="B1:B11"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="7" xr3:uid="{B7904B75-EB47-4AE0-AC16-835BCD406E73}" name="Added to Altium?" dataDxfId="25"/>
-    <tableColumn id="1" xr3:uid="{0881C807-AE0D-4E97-942D-F1BB4BC72740}" name="Name" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{FF11C1E0-268B-4AB9-A529-8334EF2C69FD}" name="# GPIO" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{55162BE7-C291-4B9F-ABE8-A7DE102A5A2F}" name="UART" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{12871EC5-67F1-442C-B9F6-E715FA2B13DA}" name="SPI" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{0676FDA2-81C4-49A9-A3D1-DEE7F28D8014}" name="I2C" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{4D86DECE-60FC-46A0-B57F-AB144D9C1459}" name="PWM" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{F498CA82-C855-4B59-BFFB-E076763E2C7B}" name="USB" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{1C8B55E3-7B48-484B-9DEC-D60D33855BF8}" name="Part Number" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{EB01044E-239A-43EB-B0C2-1F87DDB54160}" name="Description" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{B7904B75-EB47-4AE0-AC16-835BCD406E73}" name="Added to Altium?" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{0881C807-AE0D-4E97-942D-F1BB4BC72740}" name="Name" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{FF11C1E0-268B-4AB9-A529-8334EF2C69FD}" name="# GPIO" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{55162BE7-C291-4B9F-ABE8-A7DE102A5A2F}" name="UART" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{12871EC5-67F1-442C-B9F6-E715FA2B13DA}" name="SPI" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{0676FDA2-81C4-49A9-A3D1-DEE7F28D8014}" name="I2C" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{4D86DECE-60FC-46A0-B57F-AB144D9C1459}" name="PWM" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{F498CA82-C855-4B59-BFFB-E076763E2C7B}" name="USB" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{1C8B55E3-7B48-484B-9DEC-D60D33855BF8}" name="Part Number" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{EB01044E-239A-43EB-B0C2-1F87DDB54160}" name="Description" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}" name="Resistors" displayName="Resistors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}" name="Resistors" displayName="Resistors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77">
   <autoFilter ref="A1:H100" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H50">
     <sortCondition ref="C1:C50"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{5CCC4BAB-E9A7-42D2-BFCF-40A14E4FCFB3}" name="Added to Altium?" dataDxfId="13"/>
-    <tableColumn id="1" xr3:uid="{E2BB1AD3-36C9-4D80-8A78-E46D0D28B43D}" name="Resistance" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{C2F2285A-BFA3-4714-8945-6FE63C9CDE81}" name="Res (Raw)" dataDxfId="11">
+    <tableColumn id="8" xr3:uid="{5CCC4BAB-E9A7-42D2-BFCF-40A14E4FCFB3}" name="Added to Altium?" dataDxfId="76"/>
+    <tableColumn id="1" xr3:uid="{E2BB1AD3-36C9-4D80-8A78-E46D0D28B43D}" name="Resistance" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{C2F2285A-BFA3-4714-8945-6FE63C9CDE81}" name="Res (Raw)" dataDxfId="74">
       <calculatedColumnFormula>IF(ISNUMBER(B2),
 IF(B2=0,"",B2),
 VALUE(LEFT(B2,LEN(B2)-1))*
@@ -3247,11 +3340,11 @@
 IF(RIGHT(B2,1)="M",1000000,
 IF(RIGHT(B2,1)="m",0.001,1))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{67EED117-D01D-4FE8-BB40-D7D8F55BAB48}" name="Tolerance" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{F1269AFE-5CA5-4F00-93B8-6023E945504D}" name="Package" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{A4374340-1758-433F-80B6-83ABF6D97E11}" name="Wattage" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{7C53E4E9-C23D-4482-9A46-441AB8A4E1B1}" name="Part Number" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{BD8216A4-1B75-4738-A589-0D33231AD075}" name="Description" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{67EED117-D01D-4FE8-BB40-D7D8F55BAB48}" name="Tolerance" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{F1269AFE-5CA5-4F00-93B8-6023E945504D}" name="Package" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{A4374340-1758-433F-80B6-83ABF6D97E11}" name="Wattage" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{7C53E4E9-C23D-4482-9A46-441AB8A4E1B1}" name="Part Number" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{BD8216A4-1B75-4738-A589-0D33231AD075}" name="Description" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3329,20 +3422,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="64">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="69"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="65"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="64"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="63"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3365,13 +3458,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="55">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="54"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3391,8 +3484,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="52"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3402,11 +3495,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="51">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series" dataDxfId="49"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -3417,25 +3510,25 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="48">
   <autoFilter ref="A1:E11" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="56"/>
-    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="42">
   <autoFilter ref="A1:I10" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="40"/>
     <tableColumn id="4" xr3:uid="{D6AD8AA5-BC88-4F36-A647-B68EB5308316}" name="Automotive Fuse Size"/>
     <tableColumn id="1" xr3:uid="{5D9981C8-F221-4013-A9BA-4E5BF3474E5D}" name="Trip Current"/>
     <tableColumn id="2" xr3:uid="{494ED5E9-E1DA-4E76-9EAF-806837FCC14C}" name="Package"/>
@@ -3449,14 +3542,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:E11" totalsRowShown="0" headerRowDxfId="48">
-  <autoFilter ref="A1:E11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
-  <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="47"/>
-    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="39">
+  <autoFilter ref="A1:F11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
+  <tableColumns count="6">
+    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3787,83 +3881,83 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3873,140 +3967,161 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0DCFA9-0ACD-44E9-B5AC-404F4D59A007}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.54296875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.1796875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32" style="3" customWidth="1"/>
-    <col min="5" max="5" width="45.81640625" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="3" hidden="1"/>
+    <col min="2" max="3" width="15.6328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="32" style="3" customWidth="1"/>
+    <col min="6" max="6" width="45.81640625" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>214</v>
+        <v>858</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="b">
         <v>0</v>
       </c>
@@ -4036,28 +4151,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -4065,22 +4180,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
         <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -4088,22 +4203,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
         <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -4111,22 +4226,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
         <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -4134,22 +4249,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -4157,22 +4272,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
         <v>354</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -4180,25 +4295,25 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F7" t="s">
         <v>360</v>
-      </c>
-      <c r="F7" t="s">
-        <v>361</v>
       </c>
       <c r="G7">
         <v>16347</v>
       </c>
       <c r="H7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -4206,22 +4321,22 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -4229,22 +4344,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
         <v>416</v>
-      </c>
-      <c r="D9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -4252,22 +4367,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -4275,25 +4390,25 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="C11" t="s">
+        <v>361</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="C11" t="s">
-        <v>362</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
         <v>600</v>
       </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>601</v>
-      </c>
-      <c r="H11" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -4301,25 +4416,25 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
+        <v>715</v>
+      </c>
+      <c r="C12" t="s">
+        <v>415</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="C12" t="s">
-        <v>416</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" t="s">
+        <v>360</v>
+      </c>
+      <c r="G12" t="s">
         <v>717</v>
       </c>
-      <c r="F12" t="s">
-        <v>361</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>718</v>
-      </c>
-      <c r="H12" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -4384,25 +4499,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>272</v>
-      </c>
       <c r="E1" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -4410,22 +4525,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" t="s">
         <v>274</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2" t="s">
         <v>275</v>
       </c>
-      <c r="D2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>276</v>
-      </c>
-      <c r="G2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -4433,22 +4548,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" t="s">
         <v>454</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>455</v>
-      </c>
-      <c r="G3" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -4509,16 +4624,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -4526,13 +4641,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" t="s">
         <v>233</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>234</v>
-      </c>
-      <c r="D2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4540,13 +4655,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -4554,13 +4669,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" t="s">
         <v>133</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>134</v>
-      </c>
-      <c r="D4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4568,13 +4683,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" t="s">
         <v>260</v>
-      </c>
-      <c r="D5" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4582,13 +4697,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" t="s">
         <v>377</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>378</v>
-      </c>
-      <c r="D6" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4596,13 +4711,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" t="s">
         <v>501</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>502</v>
-      </c>
-      <c r="D7" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -4610,13 +4725,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C8" t="s">
+        <v>588</v>
+      </c>
+      <c r="D8" t="s">
         <v>589</v>
-      </c>
-      <c r="D8" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4624,13 +4739,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C9" t="s">
+        <v>595</v>
+      </c>
+      <c r="D9" t="s">
         <v>596</v>
-      </c>
-      <c r="D9" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -4678,28 +4793,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F1" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="G1" s="23" t="s">
         <v>489</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>490</v>
-      </c>
       <c r="H1" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -4707,25 +4822,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -4733,25 +4848,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -4817,34 +4932,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>220</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>221</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -4852,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C2" s="14">
         <v>30</v>
@@ -4873,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -4881,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="14">
         <v>48</v>
@@ -4902,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -4971,28 +5086,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -5012,19 +5127,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G2" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>426</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -5039,19 +5154,19 @@
         <v>27</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -5066,19 +5181,19 @@
         <v>33</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -5093,19 +5208,19 @@
         <v>100</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G5" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>236</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -5120,19 +5235,19 @@
         <v>120</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G6" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>545</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -5147,19 +5262,19 @@
         <v>220</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G7" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>607</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -5174,19 +5289,19 @@
         <v>220</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -5201,19 +5316,19 @@
         <v>220</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G9" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="H9" s="16" t="s">
         <v>356</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -5228,19 +5343,19 @@
         <v>680</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G10" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>441</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -5248,26 +5363,26 @@
         <v>1</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="17">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -5275,26 +5390,26 @@
         <v>1</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="17">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G12" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -5302,26 +5417,26 @@
         <v>1</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C13" s="17">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G13" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>460</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -5329,26 +5444,26 @@
         <v>1</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="17">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>65</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -5356,26 +5471,26 @@
         <v>1</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C15" s="17">
         <f t="shared" si="0"/>
         <v>3300</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G15" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="H15" s="16" t="s">
         <v>370</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -5383,26 +5498,26 @@
         <v>1</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C16" s="17">
         <f t="shared" si="0"/>
         <v>3480</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G16" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="H16" s="16" t="s">
         <v>535</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -5410,26 +5525,26 @@
         <v>1</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="17">
         <f t="shared" si="0"/>
         <v>5100</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="16" t="s">
         <v>54</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -5437,26 +5552,26 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C18" s="17">
         <f t="shared" si="0"/>
         <v>9090</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G18" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>532</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -5464,26 +5579,26 @@
         <v>1</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="17">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
       <c r="D19" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E19" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="16" t="s">
+      <c r="G19" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="H19" s="16" t="s">
         <v>139</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -5491,26 +5606,26 @@
         <v>1</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C20" s="17">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G20" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>389</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -5518,26 +5633,26 @@
         <v>1</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C21" s="17">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G21" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>439</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -5545,26 +5660,26 @@
         <v>1</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C22" s="17">
         <f t="shared" si="0"/>
         <v>47000</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G22" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="H22" s="16" t="s">
         <v>328</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -5572,26 +5687,26 @@
         <v>1</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C23" s="17">
         <f t="shared" si="0"/>
         <v>52300</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G23" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="16" t="s">
         <v>142</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -5599,26 +5714,26 @@
         <v>1</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C24" s="17">
         <f t="shared" si="0"/>
         <v>90900</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G24" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="H24" s="16" t="s">
         <v>529</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -5626,26 +5741,26 @@
         <v>1</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C25" s="17">
         <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="G25" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="H25" s="16" t="s">
         <v>263</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -5653,26 +5768,26 @@
         <v>1</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C26" s="17">
         <f t="shared" si="0"/>
         <v>200000</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G26" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>384</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -5680,26 +5795,26 @@
         <v>1</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C27" s="17">
         <f t="shared" si="0"/>
         <v>300000</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G27" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="H27" s="16" t="s">
         <v>387</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -5707,26 +5822,26 @@
         <v>1</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C28" s="17">
         <f t="shared" si="0"/>
         <v>680000</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -5734,26 +5849,26 @@
         <v>1</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C29" s="17">
         <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F29" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="G29" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="G29" s="16" t="s">
-        <v>288</v>
-      </c>
       <c r="H29" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -5761,26 +5876,26 @@
         <v>1</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C30" s="17">
         <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G30" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="H30" s="16" t="s">
         <v>321</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -5788,26 +5903,26 @@
         <v>1</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C31" s="17">
         <f t="shared" si="0"/>
         <v>392000</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G31" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="H31" s="16" t="s">
         <v>570</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -5822,19 +5937,19 @@
         <v>845</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G32" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="H32" s="16" t="s">
         <v>572</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -5849,19 +5964,19 @@
         <v>698</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G33" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="H33" s="16" t="s">
         <v>574</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -5869,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C34" s="17">
         <f t="shared" ref="C34:C97" si="1">IF(ISNUMBER(B34),
@@ -5881,19 +5996,19 @@
         <v>53200</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G34" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="H34" s="16" t="s">
         <v>580</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -5908,19 +6023,19 @@
         <v>100</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E35" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>617</v>
+      </c>
+      <c r="G35" s="16" t="s">
         <v>621</v>
       </c>
-      <c r="F35" s="16" t="s">
-        <v>618</v>
-      </c>
-      <c r="G35" s="16" t="s">
+      <c r="H35" s="16" t="s">
         <v>622</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -5935,19 +6050,19 @@
         <v>10</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G36" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="H36" s="16" t="s">
         <v>702</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -5955,26 +6070,26 @@
         <v>1</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C37" s="17">
         <f t="shared" si="1"/>
         <v>887000</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E37" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -5982,26 +6097,26 @@
         <v>1</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C38" s="17">
         <f t="shared" si="1"/>
         <v>29400</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E38" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -6009,26 +6124,26 @@
         <v>1</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C39" s="17">
         <f t="shared" si="1"/>
         <v>34000</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E39" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G39" s="16" t="s">
+        <v>786</v>
+      </c>
+      <c r="H39" s="16" t="s">
         <v>787</v>
-      </c>
-      <c r="H39" s="16" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -6036,26 +6151,26 @@
         <v>1</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C40" s="17">
         <f t="shared" si="1"/>
         <v>24000</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G40" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="H40" s="16" t="s">
         <v>790</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -6063,26 +6178,26 @@
         <v>1</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C41" s="17">
         <f t="shared" si="1"/>
         <v>56000</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -6090,26 +6205,26 @@
         <v>1</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C42" s="17">
         <f t="shared" si="1"/>
         <v>35700</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E42" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G42" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="H42" s="16" t="s">
         <v>796</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -6117,26 +6232,26 @@
         <v>1</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C43" s="17">
         <f t="shared" si="1"/>
         <v>499000</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E43" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G43" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="H43" s="16" t="s">
         <v>799</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -6144,26 +6259,26 @@
         <v>1</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C44" s="17">
         <f t="shared" si="1"/>
         <v>4870</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G44" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="H44" s="16" t="s">
         <v>802</v>
-      </c>
-      <c r="H44" s="16" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -6171,26 +6286,26 @@
         <v>1</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C45" s="17">
         <f t="shared" si="1"/>
         <v>8250</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E45" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G45" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="H45" s="16" t="s">
         <v>805</v>
-      </c>
-      <c r="H45" s="16" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -6198,61 +6313,81 @@
         <v>1</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C46" s="17">
         <f t="shared" si="1"/>
         <v>681000</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="B47" s="15">
-        <v>0</v>
-      </c>
-      <c r="C47" s="17" t="str">
+        <v>1</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>859</v>
+      </c>
+      <c r="C47" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
+        <v>30100</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>860</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>861</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="B48" s="15">
-        <v>0</v>
-      </c>
-      <c r="C48" s="17" t="str">
+        <v>1</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>862</v>
+      </c>
+      <c r="C48" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
+        <v>422000</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>863</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>864</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="18" t="b">
@@ -7168,25 +7303,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" t="s">
         <v>70</v>
       </c>
-      <c r="F1" t="s">
-        <v>71</v>
-      </c>
       <c r="G1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -7194,22 +7329,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
         <v>73</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>74</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>75</v>
       </c>
-      <c r="F2" t="s">
-        <v>76</v>
-      </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -7217,22 +7352,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" t="s">
         <v>310</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>311</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>312</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" t="s">
         <v>313</v>
-      </c>
-      <c r="F3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -7240,22 +7375,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" t="s">
         <v>391</v>
       </c>
-      <c r="C4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>392</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>393</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>394</v>
-      </c>
-      <c r="G4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -7263,16 +7398,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
+        <v>412</v>
+      </c>
+      <c r="G5" t="s">
         <v>413</v>
-      </c>
-      <c r="G5" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -7280,22 +7415,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>602</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
         <v>603</v>
       </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" t="s">
         <v>604</v>
       </c>
-      <c r="E6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>605</v>
-      </c>
-      <c r="G6" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -7303,22 +7438,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>833</v>
+      </c>
+      <c r="C7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" t="s">
         <v>834</v>
       </c>
-      <c r="C7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" t="s">
         <v>835</v>
       </c>
-      <c r="E7" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>836</v>
-      </c>
-      <c r="G7" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -7366,22 +7501,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -7389,19 +7524,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -7409,19 +7544,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E3">
         <v>5012</v>
       </c>
       <c r="F3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -7488,31 +7623,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>296</v>
-      </c>
       <c r="D1" s="21" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1" s="21" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -7520,25 +7655,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" t="s">
         <v>299</v>
       </c>
-      <c r="D2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" t="s">
         <v>300</v>
       </c>
-      <c r="G2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>301</v>
-      </c>
-      <c r="I2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -7546,28 +7681,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F3" t="s">
+        <v>584</v>
+      </c>
+      <c r="G3" t="s">
         <v>585</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>586</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>587</v>
-      </c>
-      <c r="I3" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -7575,28 +7710,28 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E4" t="s">
+        <v>591</v>
+      </c>
+      <c r="F4" t="s">
         <v>592</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>590</v>
+      </c>
+      <c r="H4" t="s">
         <v>593</v>
       </c>
-      <c r="G4" t="s">
-        <v>591</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>594</v>
-      </c>
-      <c r="I4" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -7604,28 +7739,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>695</v>
+      </c>
+      <c r="C5" t="s">
+        <v>694</v>
+      </c>
+      <c r="D5" t="s">
+        <v>738</v>
+      </c>
+      <c r="E5" t="s">
+        <v>740</v>
+      </c>
+      <c r="F5" t="s">
         <v>696</v>
       </c>
-      <c r="C5" t="s">
-        <v>695</v>
-      </c>
-      <c r="D5" t="s">
-        <v>739</v>
-      </c>
-      <c r="E5" t="s">
-        <v>741</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>697</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>699</v>
+      </c>
+      <c r="I5" t="s">
         <v>698</v>
-      </c>
-      <c r="H5" t="s">
-        <v>700</v>
-      </c>
-      <c r="I5" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -7633,28 +7768,28 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C6" t="s">
+        <v>734</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="F6" t="s">
+        <v>742</v>
+      </c>
+      <c r="G6" t="s">
+        <v>590</v>
+      </c>
+      <c r="H6" t="s">
         <v>735</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
         <v>743</v>
-      </c>
-      <c r="G6" t="s">
-        <v>591</v>
-      </c>
-      <c r="H6" t="s">
-        <v>736</v>
-      </c>
-      <c r="I6" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -7662,28 +7797,28 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
+        <v>771</v>
+      </c>
+      <c r="F7" t="s">
         <v>772</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>773</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>770</v>
+      </c>
+      <c r="I7" t="s">
         <v>774</v>
-      </c>
-      <c r="H7" t="s">
-        <v>771</v>
-      </c>
-      <c r="I7" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -7691,28 +7826,28 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
+        <v>775</v>
+      </c>
+      <c r="F8" t="s">
         <v>776</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>820</v>
+      </c>
+      <c r="H8" t="s">
         <v>777</v>
       </c>
-      <c r="G8" t="s">
-        <v>821</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>778</v>
-      </c>
-      <c r="I8" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -7720,28 +7855,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E9" t="s">
+        <v>818</v>
+      </c>
+      <c r="F9" t="s">
         <v>819</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>820</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>821</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>822</v>
-      </c>
-      <c r="I9" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -7925,7 +8060,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -7937,13 +8072,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -7963,22 +8098,22 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" s="5">
         <v>0.1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -7986,28 +8121,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H3" t="s">
         <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -8015,28 +8150,28 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -8044,28 +8179,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="E5" s="5">
         <v>0.1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -8073,28 +8208,28 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E6" s="5">
         <v>0.1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -8102,28 +8237,28 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
         <v>106</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>107</v>
       </c>
       <c r="E7" s="5">
         <v>0.1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H7" t="s">
         <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -8131,28 +8266,28 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="E8" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>199</v>
       </c>
       <c r="H8" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -8160,28 +8295,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>293</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="E9" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H9" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>111</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -8189,28 +8324,28 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E10" s="5">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H10" t="s">
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -8218,28 +8353,28 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="E11" s="5">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>199</v>
       </c>
       <c r="H11" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I11" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -8247,28 +8382,28 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>343</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>344</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5">
         <v>0.2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H12" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="I12" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -8276,28 +8411,28 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>399</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="E13" s="5">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H13" t="s">
         <v>9</v>
       </c>
       <c r="I13" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -8305,28 +8440,28 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" s="5">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H14" t="s">
         <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -8334,28 +8469,28 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="E15" s="5">
         <v>0.2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>199</v>
       </c>
       <c r="H15" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I15" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -8363,25 +8498,25 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>428</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c r="E16" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="I16" t="s">
         <v>429</v>
@@ -8392,28 +8527,28 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>430</v>
       </c>
       <c r="E17" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>199</v>
       </c>
       <c r="H17" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -8421,28 +8556,28 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>456</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>431</v>
+        <v>106</v>
       </c>
       <c r="E18" s="5">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="I18" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -8450,28 +8585,28 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>457</v>
+        <v>293</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="E19" s="5">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>458</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -8479,28 +8614,28 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>294</v>
+        <v>504</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="E20" s="5">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H20" t="s">
         <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -8508,28 +8643,28 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21" s="5">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H21" t="s">
         <v>9</v>
       </c>
       <c r="I21" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -8537,28 +8672,28 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E22" s="5">
         <v>0.1</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H22" t="s">
         <v>9</v>
       </c>
       <c r="I22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -8566,28 +8701,28 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>516</v>
+        <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>8</v>
+        <v>557</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="E23" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>199</v>
       </c>
       <c r="H23" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I23" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -8595,28 +8730,28 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>566</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>558</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>344</v>
+        <v>17</v>
       </c>
       <c r="E24" s="5">
         <v>0.2</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H24" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -8624,28 +8759,28 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>567</v>
+        <v>105</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H25" t="s">
         <v>9</v>
       </c>
       <c r="I25" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -8653,28 +8788,28 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>627</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="E26" s="5">
         <v>0.1</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H26" t="s">
         <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>582</v>
+        <v>628</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -8682,28 +8817,28 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>628</v>
+        <v>660</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>8</v>
+        <v>557</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="E27" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>199</v>
       </c>
       <c r="H27" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="I27" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -8711,28 +8846,28 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>558</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>344</v>
+        <v>17</v>
       </c>
       <c r="E28" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -8740,28 +8875,28 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>678</v>
+        <v>293</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E29" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>199</v>
       </c>
       <c r="H29" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" t="s">
-        <v>679</v>
+        <v>112</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -8769,38 +8904,86 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>294</v>
+        <v>848</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="E30" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H30" t="s">
-        <v>113</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>770</v>
+        <v>9</v>
+      </c>
+      <c r="I30" t="s">
+        <v>847</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>865</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
@@ -8883,16 +9066,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8915,25 +9094,25 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H1" t="s">
         <v>3</v>
@@ -8942,7 +9121,7 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -8950,28 +9129,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" t="s">
         <v>227</v>
-      </c>
-      <c r="E2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -8979,31 +9158,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" t="s">
         <v>365</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" t="s">
+        <v>814</v>
+      </c>
+      <c r="I3" t="s">
         <v>366</v>
       </c>
-      <c r="F3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H3" t="s">
-        <v>815</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>367</v>
-      </c>
-      <c r="J3" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -9011,28 +9190,28 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E4" t="s">
+        <v>371</v>
+      </c>
+      <c r="F4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" t="s">
         <v>373</v>
       </c>
-      <c r="E4" t="s">
-        <v>372</v>
-      </c>
-      <c r="F4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>374</v>
-      </c>
-      <c r="J4" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -9040,28 +9219,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D5" t="s">
+        <v>623</v>
+      </c>
+      <c r="E5" t="s">
+        <v>604</v>
+      </c>
+      <c r="F5" t="s">
         <v>624</v>
       </c>
-      <c r="E5" t="s">
-        <v>605</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" t="s">
         <v>625</v>
       </c>
-      <c r="G5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>626</v>
-      </c>
-      <c r="J5" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -9069,28 +9248,28 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
+        <v>729</v>
+      </c>
+      <c r="G6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" t="s">
         <v>730</v>
       </c>
-      <c r="G6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>731</v>
-      </c>
-      <c r="J6" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -9098,28 +9277,28 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I7" t="s">
+        <v>732</v>
+      </c>
+      <c r="J7" t="s">
         <v>733</v>
-      </c>
-      <c r="J7" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -9127,31 +9306,31 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" t="s">
         <v>144</v>
       </c>
-      <c r="C8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" t="s">
+        <v>815</v>
+      </c>
+      <c r="I8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J8" t="s">
         <v>147</v>
-      </c>
-      <c r="F8" t="s">
-        <v>145</v>
-      </c>
-      <c r="G8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H8" t="s">
-        <v>816</v>
-      </c>
-      <c r="I8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J8" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -9159,28 +9338,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F9" t="s">
+        <v>392</v>
+      </c>
+      <c r="G9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" t="s">
         <v>553</v>
       </c>
-      <c r="F9" t="s">
-        <v>393</v>
-      </c>
-      <c r="G9" t="s">
-        <v>104</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>554</v>
-      </c>
-      <c r="J9" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -9188,28 +9367,28 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
+        <v>657</v>
+      </c>
+      <c r="E10" t="s">
+        <v>604</v>
+      </c>
+      <c r="F10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" t="s">
         <v>658</v>
       </c>
-      <c r="E10" t="s">
-        <v>605</v>
-      </c>
-      <c r="F10" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>659</v>
-      </c>
-      <c r="J10" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -9217,36 +9396,63 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D11" t="s">
+        <v>811</v>
+      </c>
+      <c r="E11" t="s">
         <v>812</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>810</v>
+      </c>
+      <c r="G11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" t="s">
+        <v>815</v>
+      </c>
+      <c r="I11" t="s">
+        <v>809</v>
+      </c>
+      <c r="J11" t="s">
         <v>813</v>
-      </c>
-      <c r="F11" t="s">
-        <v>811</v>
-      </c>
-      <c r="G11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H11" t="s">
-        <v>816</v>
-      </c>
-      <c r="I11" t="s">
-        <v>810</v>
-      </c>
-      <c r="J11" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="b">
         <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" t="s">
+        <v>851</v>
+      </c>
+      <c r="E12" t="s">
+        <v>852</v>
+      </c>
+      <c r="F12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" t="s">
+        <v>853</v>
+      </c>
+      <c r="I12" t="s">
+        <v>849</v>
+      </c>
+      <c r="J12" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -9369,28 +9575,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -9398,19 +9604,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C2" s="12">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -9418,22 +9624,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C3" s="12">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -9441,22 +9647,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C4" s="12">
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -9464,13 +9670,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C5" s="12">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -9478,13 +9684,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C6" s="12">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -9492,13 +9698,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="12">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -9506,13 +9712,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C8" s="12">
         <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -9520,13 +9726,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C9" s="12">
         <v>6</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -9534,13 +9740,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C10" s="12">
         <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -9548,13 +9754,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C11" s="12">
         <v>10</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -9562,13 +9768,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C12" s="12">
         <v>24</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -9576,13 +9782,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C13" s="12">
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -9590,22 +9796,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C14" s="12">
         <v>3</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -9613,16 +9819,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C15" s="12">
         <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -9630,19 +9836,19 @@
         <v>1</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="C16" s="12">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -9650,19 +9856,19 @@
         <v>1</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C17" s="12">
         <v>1</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -9670,25 +9876,25 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C18" s="12">
         <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>446</v>
-      </c>
       <c r="H18" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -9696,25 +9902,25 @@
         <v>1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C19" s="12">
         <v>12</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -9722,19 +9928,19 @@
         <v>1</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C20" s="12">
         <v>20</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -9742,22 +9948,22 @@
         <v>1</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C21" s="12">
         <v>20</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -9765,22 +9971,22 @@
         <v>1</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C22" s="12">
         <v>30</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="H22" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -9788,25 +9994,25 @@
         <v>1</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C23" s="12">
         <v>30</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -9814,22 +10020,22 @@
         <v>1</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C24" s="12">
         <v>2</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -9837,22 +10043,22 @@
         <v>1</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C25" s="12">
         <v>3</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -9860,19 +10066,19 @@
         <v>1</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C26" s="12">
         <v>4</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -9880,19 +10086,19 @@
         <v>1</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C27" s="12">
         <v>6</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -9900,22 +10106,22 @@
         <v>1</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C28" s="12">
         <v>16</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -9923,25 +10129,25 @@
         <v>1</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C29" s="12">
         <v>8</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -9949,25 +10155,25 @@
         <v>1</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C30" s="12">
         <v>3</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -9975,25 +10181,25 @@
         <v>1</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C31" s="12">
         <v>2</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>651</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -10001,19 +10207,19 @@
         <v>1</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C32" s="12">
         <v>10</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -10021,16 +10227,16 @@
         <v>1</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C33" s="12">
         <v>16</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -10038,19 +10244,19 @@
         <v>1</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C34" s="12">
         <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -10058,19 +10264,19 @@
         <v>1</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C35" s="12">
         <v>3</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -10078,19 +10284,19 @@
         <v>1</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C36" s="12">
         <v>4</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -10098,19 +10304,19 @@
         <v>1</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C37" s="12">
         <v>5</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -10118,19 +10324,19 @@
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" s="12">
         <v>6</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -10138,13 +10344,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C39" s="12">
         <v>10</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -10152,19 +10358,19 @@
         <v>1</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C40" s="12">
         <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -10172,22 +10378,22 @@
         <v>1</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C41" s="12">
         <v>2</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -10195,22 +10401,22 @@
         <v>1</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C42" s="12">
         <v>3</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -10218,22 +10424,22 @@
         <v>1</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C43" s="12">
         <v>4</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -10241,22 +10447,22 @@
         <v>1</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C44" s="12">
         <v>3</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -10264,22 +10470,22 @@
         <v>1</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C45" s="12">
         <v>2</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -10287,22 +10493,22 @@
         <v>1</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C46" s="12">
         <v>4</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="G46" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -10310,22 +10516,22 @@
         <v>1</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C47" s="12">
         <v>8</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -10333,22 +10539,22 @@
         <v>1</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C48" s="12">
         <v>4</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -10356,19 +10562,19 @@
         <v>1</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C49" s="12">
         <v>5</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -10376,20 +10582,20 @@
         <v>1</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C50" s="12"/>
       <c r="D50" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -10397,25 +10603,25 @@
         <v>1</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C51" s="12">
         <v>20</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="G51" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -10423,22 +10629,22 @@
         <v>1</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C52" s="12">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="C52" s="12">
-        <v>1</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="G52" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -10446,22 +10652,22 @@
         <v>1</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C53" s="12">
         <v>4</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -10469,35 +10675,75 @@
         <v>1</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C54" s="12">
         <v>8</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E54" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C55" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="C55" s="12">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C56" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="C56" s="12">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="b">
@@ -10790,25 +11036,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
         <v>97</v>
       </c>
-      <c r="C1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" t="s">
-        <v>98</v>
-      </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -10816,22 +11062,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
         <v>99</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>100</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" t="s">
         <v>101</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>104</v>
-      </c>
-      <c r="F2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -10839,22 +11085,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" t="s">
         <v>162</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>160</v>
-      </c>
-      <c r="E3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -10862,22 +11108,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
+        <v>546</v>
+      </c>
+      <c r="G4" t="s">
         <v>547</v>
-      </c>
-      <c r="G4" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -10967,28 +11213,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -10996,25 +11242,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" t="s">
         <v>170</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>171</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F2" t="s">
         <v>172</v>
       </c>
-      <c r="E2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>173</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>174</v>
-      </c>
-      <c r="H2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -11022,22 +11268,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
         <v>117</v>
       </c>
-      <c r="C3" t="s">
-        <v>118</v>
-      </c>
       <c r="D3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" t="s">
+        <v>670</v>
+      </c>
+      <c r="F3" t="s">
         <v>120</v>
       </c>
-      <c r="E3" t="s">
-        <v>671</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>121</v>
-      </c>
-      <c r="G3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -11045,25 +11291,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" t="s">
         <v>117</v>
       </c>
-      <c r="C4" t="s">
-        <v>118</v>
-      </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F4" t="s">
+        <v>464</v>
+      </c>
+      <c r="G4" t="s">
         <v>465</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>466</v>
-      </c>
-      <c r="H4" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -11071,25 +11317,25 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
+        <v>666</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>669</v>
+      </c>
+      <c r="F5" t="s">
+        <v>469</v>
+      </c>
+      <c r="G5" t="s">
         <v>667</v>
       </c>
-      <c r="D5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" t="s">
-        <v>670</v>
-      </c>
-      <c r="F5" t="s">
-        <v>470</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>668</v>
-      </c>
-      <c r="H5" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -11097,22 +11343,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>523</v>
+      </c>
+      <c r="C6" t="s">
         <v>524</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
+        <v>618</v>
+      </c>
+      <c r="F6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" t="s">
         <v>525</v>
       </c>
-      <c r="E6" t="s">
-        <v>619</v>
-      </c>
-      <c r="F6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>526</v>
-      </c>
-      <c r="H6" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -11120,22 +11366,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C7" t="s">
+        <v>632</v>
+      </c>
+      <c r="E7" t="s">
+        <v>636</v>
+      </c>
+      <c r="F7" t="s">
+        <v>634</v>
+      </c>
+      <c r="G7" t="s">
         <v>633</v>
       </c>
-      <c r="E7" t="s">
-        <v>637</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>635</v>
-      </c>
-      <c r="G7" t="s">
-        <v>634</v>
-      </c>
-      <c r="H7" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -11143,22 +11389,22 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C8" t="s">
         <v>468</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
+        <v>617</v>
+      </c>
+      <c r="F8" t="s">
         <v>469</v>
       </c>
-      <c r="E8" t="s">
-        <v>618</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>470</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>471</v>
-      </c>
-      <c r="H8" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -11166,22 +11412,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C9" t="s">
         <v>468</v>
       </c>
-      <c r="C9" t="s">
-        <v>469</v>
-      </c>
       <c r="E9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G9" t="s">
+        <v>608</v>
+      </c>
+      <c r="H9" t="s">
         <v>609</v>
-      </c>
-      <c r="H9" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -11189,22 +11435,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C10" t="s">
+        <v>613</v>
+      </c>
+      <c r="E10" t="s">
+        <v>617</v>
+      </c>
+      <c r="F10" t="s">
         <v>614</v>
       </c>
-      <c r="E10" t="s">
-        <v>618</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>615</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>616</v>
-      </c>
-      <c r="H10" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -11212,22 +11458,22 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E11" t="s">
+        <v>617</v>
+      </c>
+      <c r="F11" t="s">
+        <v>614</v>
+      </c>
+      <c r="G11" t="s">
         <v>630</v>
       </c>
-      <c r="E11" t="s">
-        <v>618</v>
-      </c>
-      <c r="F11" t="s">
-        <v>615</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>631</v>
-      </c>
-      <c r="H11" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11235,22 +11481,22 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C12" t="s">
+        <v>764</v>
+      </c>
+      <c r="E12" t="s">
         <v>765</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>766</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>767</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>768</v>
-      </c>
-      <c r="H12" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -11258,22 +11504,22 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
+        <v>523</v>
+      </c>
+      <c r="C13" t="s">
         <v>524</v>
       </c>
-      <c r="C13" t="s">
-        <v>525</v>
-      </c>
       <c r="E13" t="s">
+        <v>765</v>
+      </c>
+      <c r="F13" t="s">
         <v>766</v>
       </c>
-      <c r="F13" t="s">
-        <v>767</v>
-      </c>
       <c r="G13" t="s">
+        <v>816</v>
+      </c>
+      <c r="H13" t="s">
         <v>817</v>
-      </c>
-      <c r="H13" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -11334,19 +11580,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -11354,16 +11600,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D2" t="s">
         <v>638</v>
       </c>
-      <c r="C2" t="s">
-        <v>647</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>639</v>
-      </c>
-      <c r="E2" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -11371,16 +11617,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D3" t="s">
+        <v>647</v>
+      </c>
+      <c r="E3" t="s">
         <v>648</v>
-      </c>
-      <c r="E3" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -11388,16 +11634,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4" t="s">
+        <v>422</v>
+      </c>
+      <c r="D4" t="s">
         <v>420</v>
       </c>
-      <c r="C4" t="s">
-        <v>423</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>421</v>
-      </c>
-      <c r="E4" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -11405,13 +11651,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D5" t="s">
+        <v>612</v>
+      </c>
+      <c r="E5" t="s">
         <v>611</v>
-      </c>
-      <c r="D5" t="s">
-        <v>613</v>
-      </c>
-      <c r="E5" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -11419,16 +11665,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>507</v>
+      </c>
+      <c r="C6" t="s">
         <v>508</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>509</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>510</v>
-      </c>
-      <c r="E6" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -11436,16 +11682,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>673</v>
+      </c>
+      <c r="C7" t="s">
+        <v>676</v>
+      </c>
+      <c r="D7" t="s">
         <v>674</v>
       </c>
-      <c r="C7" t="s">
-        <v>677</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>675</v>
-      </c>
-      <c r="E7" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -11453,13 +11699,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" t="s">
         <v>168</v>
-      </c>
-      <c r="E8" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -11467,16 +11713,16 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>707</v>
+      </c>
+      <c r="C9" t="s">
         <v>708</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>709</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>710</v>
-      </c>
-      <c r="E9" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -11484,16 +11730,16 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>540</v>
+      </c>
+      <c r="C10" t="s">
         <v>541</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>542</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>543</v>
-      </c>
-      <c r="E10" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -11501,13 +11747,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
+        <v>307</v>
+      </c>
+      <c r="D11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11" t="s">
         <v>308</v>
-      </c>
-      <c r="D11" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -11515,16 +11761,16 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
+        <v>562</v>
+      </c>
+      <c r="C12" t="s">
         <v>563</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>564</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>565</v>
-      </c>
-      <c r="E12" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -11532,16 +11778,16 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
+        <v>679</v>
+      </c>
+      <c r="C13" t="s">
         <v>680</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>681</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>682</v>
-      </c>
-      <c r="E13" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -11549,16 +11795,16 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C14" t="s">
+        <v>689</v>
+      </c>
+      <c r="D14" t="s">
         <v>690</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>691</v>
-      </c>
-      <c r="E14" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -11566,16 +11812,16 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
+        <v>719</v>
+      </c>
+      <c r="C15" t="s">
         <v>720</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>721</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>722</v>
-      </c>
-      <c r="E15" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -11583,16 +11829,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
+        <v>725</v>
+      </c>
+      <c r="C16" t="s">
         <v>726</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>727</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>728</v>
-      </c>
-      <c r="E16" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -11600,13 +11846,13 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
+        <v>559</v>
+      </c>
+      <c r="D17" t="s">
         <v>560</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>561</v>
-      </c>
-      <c r="E17" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -11614,16 +11860,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
+        <v>744</v>
+      </c>
+      <c r="C18" t="s">
+        <v>746</v>
+      </c>
+      <c r="D18" t="s">
         <v>745</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>747</v>
-      </c>
-      <c r="D18" t="s">
-        <v>746</v>
-      </c>
-      <c r="E18" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -11631,16 +11877,16 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
         <v>77</v>
-      </c>
-      <c r="E19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -11648,16 +11894,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
+        <v>379</v>
+      </c>
+      <c r="D20" t="s">
         <v>380</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>381</v>
-      </c>
-      <c r="E20" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -11665,16 +11911,16 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
+        <v>703</v>
+      </c>
+      <c r="C21" t="s">
         <v>704</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>706</v>
+      </c>
+      <c r="E21" t="s">
         <v>705</v>
-      </c>
-      <c r="D21" t="s">
-        <v>707</v>
-      </c>
-      <c r="E21" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -11682,13 +11928,13 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
+        <v>472</v>
+      </c>
+      <c r="D22" t="s">
         <v>473</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>474</v>
-      </c>
-      <c r="E22" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -11696,16 +11942,16 @@
         <v>1</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
         <v>91</v>
-      </c>
-      <c r="E23" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -11713,16 +11959,16 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C24" t="s">
+        <v>519</v>
+      </c>
+      <c r="D24" t="s">
         <v>337</v>
       </c>
-      <c r="C24" t="s">
-        <v>520</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>338</v>
-      </c>
-      <c r="E24" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -11730,16 +11976,16 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C25" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D25" t="s">
+        <v>521</v>
+      </c>
+      <c r="E25" t="s">
         <v>522</v>
-      </c>
-      <c r="E25" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -11747,16 +11993,16 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
+        <v>536</v>
+      </c>
+      <c r="C26" t="s">
+        <v>538</v>
+      </c>
+      <c r="D26" t="s">
         <v>537</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>539</v>
-      </c>
-      <c r="D26" t="s">
-        <v>538</v>
-      </c>
-      <c r="E26" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -11764,16 +12010,16 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27" t="s">
         <v>315</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>316</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>317</v>
-      </c>
-      <c r="E27" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -11781,16 +12027,16 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
+        <v>322</v>
+      </c>
+      <c r="C28" t="s">
         <v>323</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>324</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>325</v>
-      </c>
-      <c r="E28" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -11798,13 +12044,13 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
+        <v>749</v>
+      </c>
+      <c r="D29" t="s">
+        <v>748</v>
+      </c>
+      <c r="E29" t="s">
         <v>750</v>
-      </c>
-      <c r="D29" t="s">
-        <v>749</v>
-      </c>
-      <c r="E29" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -11812,16 +12058,16 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
+        <v>752</v>
+      </c>
+      <c r="C30" t="s">
         <v>753</v>
       </c>
-      <c r="C30" t="s">
-        <v>754</v>
-      </c>
       <c r="D30" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E30" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -11829,16 +12075,16 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
+        <v>755</v>
+      </c>
+      <c r="C31" t="s">
+        <v>753</v>
+      </c>
+      <c r="D31" t="s">
+        <v>754</v>
+      </c>
+      <c r="E31" t="s">
         <v>756</v>
-      </c>
-      <c r="C31" t="s">
-        <v>754</v>
-      </c>
-      <c r="D31" t="s">
-        <v>755</v>
-      </c>
-      <c r="E31" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -11846,16 +12092,16 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D32" t="s">
+        <v>758</v>
+      </c>
+      <c r="E32" t="s">
         <v>759</v>
-      </c>
-      <c r="E32" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -11863,16 +12109,16 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C33" t="s">
+        <v>762</v>
+      </c>
+      <c r="D33" t="s">
+        <v>761</v>
+      </c>
+      <c r="E33" t="s">
         <v>763</v>
-      </c>
-      <c r="D33" t="s">
-        <v>762</v>
-      </c>
-      <c r="E33" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -11985,22 +12231,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -12008,16 +12254,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" t="s">
         <v>245</v>
       </c>
-      <c r="C2" t="s">
-        <v>246</v>
-      </c>
       <c r="D2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2" t="s">
         <v>248</v>
-      </c>
-      <c r="F2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -12025,19 +12271,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" t="s">
         <v>251</v>
       </c>
-      <c r="D3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>252</v>
-      </c>
-      <c r="F3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -12045,16 +12291,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F4" t="s">
         <v>254</v>
-      </c>
-      <c r="D4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -12062,16 +12308,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" t="s">
         <v>256</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" t="s">
         <v>257</v>
-      </c>
-      <c r="D5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -12079,16 +12325,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" t="s">
         <v>404</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>405</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>406</v>
-      </c>
-      <c r="E6" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -12096,16 +12342,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C7" t="s">
         <v>434</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>435</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>436</v>
-      </c>
-      <c r="E7" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12113,16 +12359,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>824</v>
+      </c>
+      <c r="C8" t="s">
         <v>825</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>826</v>
       </c>
-      <c r="D8" t="s">
-        <v>827</v>
-      </c>
       <c r="F8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12130,13 +12376,13 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C9" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D9" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12144,16 +12390,16 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C10" t="s">
         <v>838</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>840</v>
+      </c>
+      <c r="E10" t="s">
         <v>839</v>
-      </c>
-      <c r="D10" t="s">
-        <v>841</v>
-      </c>
-      <c r="E10" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12379,7 +12625,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>2</v>
@@ -12388,10 +12634,10 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -12399,16 +12645,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3">
         <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -12481,16 +12727,16 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
@@ -12499,13 +12745,13 @@
         <v>1</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -12513,25 +12759,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2">
         <v>1812</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -12539,19 +12785,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -12559,25 +12805,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" t="s">
         <v>282</v>
-      </c>
-      <c r="G4" t="s">
-        <v>283</v>
       </c>
       <c r="H4">
         <v>3568</v>
       </c>
       <c r="I4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5F6B6F-6E3B-4E75-9446-CFB734BE530D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB77531-BB17-43DB-8EB8-BF3D267EFD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="1" activeTab="2" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="6" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome!" sheetId="15" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="892">
   <si>
     <t>Capacitance</t>
   </si>
@@ -1669,30 +1669,9 @@
     <t>3.48 kOhms ±1% 0.1W, 1/10W Chip Resistor 0603 (1608 Metric) Automotive AEC-Q200 Thick Film</t>
   </si>
   <si>
-    <t>SPI-CAN Bridge</t>
-  </si>
-  <si>
-    <t>MCP2518FDT-E/SL</t>
-  </si>
-  <si>
     <t>Uses single-ended CAN</t>
   </si>
   <si>
-    <t>CAN Controller CAN 2.0 SPI Interface 14-SOIC</t>
-  </si>
-  <si>
-    <t>CAN Frontend Transceiver</t>
-  </si>
-  <si>
-    <t>Single-ended CAN to CAN FD</t>
-  </si>
-  <si>
-    <t>ATA6561-GAQW-N</t>
-  </si>
-  <si>
-    <t>1/1 Transceiver CANbus 8-SO</t>
-  </si>
-  <si>
     <t>RC0603FR-07120RL</t>
   </si>
   <si>
@@ -2675,6 +2654,87 @@
   </si>
   <si>
     <t>Aluminum Unthreaded Spacer</t>
+  </si>
+  <si>
+    <t>Pogo</t>
+  </si>
+  <si>
+    <t>5358</t>
+  </si>
+  <si>
+    <t>Magnetic Right-Angle Thru-Hole</t>
+  </si>
+  <si>
+    <t>4 Position Spring Piston Connector Panel Mount; Through Hole, Right Angle</t>
+  </si>
+  <si>
+    <t>6.8uH</t>
+  </si>
+  <si>
+    <t>6.9A</t>
+  </si>
+  <si>
+    <t>SMD 8.50 x 8.00mm</t>
+  </si>
+  <si>
+    <t>6.8 µH Shielded Drum Core, Wirewound Inductor 6.9 A 25.85mOhm Max 2-SMD, J-Lead</t>
+  </si>
+  <si>
+    <t>ETQ-P4M6R8KVK</t>
+  </si>
+  <si>
+    <t>158k</t>
+  </si>
+  <si>
+    <t>RC0603FR-07158KL</t>
+  </si>
+  <si>
+    <t>158 kOhms ±1% 0.1W, 1/10W Chip Resistor 0603 (1608 Metric) Moisture Resistant Thick Film</t>
+  </si>
+  <si>
+    <t>MCP2515T-I/SO</t>
+  </si>
+  <si>
+    <t>CANbus Controller CAN 2.0 SPI Interface 18-SOIC</t>
+  </si>
+  <si>
+    <t>CAN-SPI Bridge</t>
+  </si>
+  <si>
+    <t>TJA1050T/CM,118</t>
+  </si>
+  <si>
+    <t>1/1 Transceiver Half CANbus 8-SO</t>
+  </si>
+  <si>
+    <t>CAN FD Front End</t>
+  </si>
+  <si>
+    <t>8MHz</t>
+  </si>
+  <si>
+    <t>18pF</t>
+  </si>
+  <si>
+    <t>ABM3-8.000MHZ-D2Y-T</t>
+  </si>
+  <si>
+    <t>8 MHz ±20ppm Crystal 18pF 140 Ohms 2-SMD, No Lead</t>
+  </si>
+  <si>
+    <t>WCS1600</t>
+  </si>
+  <si>
+    <t>Series / Purpose</t>
+  </si>
+  <si>
+    <t>Current Monitor</t>
+  </si>
+  <si>
+    <t>Hall Effect</t>
+  </si>
+  <si>
+    <t>https://www.winson.com.tw/uploads/images/WCS1600.pdf</t>
   </si>
 </sst>
 </file>
@@ -2857,6 +2917,57 @@
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3126,57 +3237,6 @@
         </ext>
       </extLst>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3221,13 +3281,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
   <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="78"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="77"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="66"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="76"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="75"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3239,11 +3299,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:H20" totalsRowShown="0">
   <autoFilter ref="A1:H20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="41"/>
     <tableColumn id="1" xr3:uid="{727DF6C0-6BC9-4CBC-ACBD-F7D7801F3DED}" name="Color"/>
     <tableColumn id="6" xr3:uid="{2F89F121-2031-4E76-8B64-C6BE1AC4E5A7}" name="Mount Type"/>
-    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="40"/>
     <tableColumn id="3" xr3:uid="{95A3DF17-FA71-419C-9869-87ACAC774187}" name="Dome"/>
     <tableColumn id="4" xr3:uid="{30ACC022-FAF3-44FA-97E2-DA5C989B54D7}" name="Part Number"/>
     <tableColumn id="5" xr3:uid="{BDED051F-FA40-461B-85BB-40EDC316E70C}" name="Description"/>
@@ -3253,10 +3313,10 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="39">
   <autoFilter ref="A1:G10" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}"/>
   <tableColumns count="7">
-    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="38"/>
     <tableColumn id="2" xr3:uid="{D4673AC2-9436-437D-9DE0-521034F11263}" name="Memory Organization"/>
     <tableColumn id="6" xr3:uid="{088605FE-5C4A-4A9F-9607-7699E9A0ED47}" name="Total Capacity"/>
     <tableColumn id="7" xr3:uid="{E9CAAB16-100E-4178-A533-7FCE76F08C9F}" name="Interface"/>
@@ -3275,7 +3335,7 @@
     <sortCondition ref="B1:B13"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="37"/>
     <tableColumn id="1" xr3:uid="{07652CF2-D7CA-452D-A87D-CEBA35FEC12A}" name="Function"/>
     <tableColumn id="2" xr3:uid="{A9FCB299-A552-4123-B45A-F31F0DC5BB9B}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{2F50D30B-F60A-4BAF-AE6D-0A3909047904}" name="Description"/>
@@ -3285,54 +3345,54 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="A1:H11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="8">
-    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="24"/>
-    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}" name="MCUs" displayName="MCUs" ref="A1:J11" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}" name="MCUs" displayName="MCUs" ref="A1:J11" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:J11" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J11">
     <sortCondition ref="B1:B11"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="7" xr3:uid="{B7904B75-EB47-4AE0-AC16-835BCD406E73}" name="Added to Altium?" dataDxfId="15"/>
-    <tableColumn id="1" xr3:uid="{0881C807-AE0D-4E97-942D-F1BB4BC72740}" name="Name" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{FF11C1E0-268B-4AB9-A529-8334EF2C69FD}" name="# GPIO" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{55162BE7-C291-4B9F-ABE8-A7DE102A5A2F}" name="UART" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{12871EC5-67F1-442C-B9F6-E715FA2B13DA}" name="SPI" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{0676FDA2-81C4-49A9-A3D1-DEE7F28D8014}" name="I2C" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{4D86DECE-60FC-46A0-B57F-AB144D9C1459}" name="PWM" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{F498CA82-C855-4B59-BFFB-E076763E2C7B}" name="USB" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{1C8B55E3-7B48-484B-9DEC-D60D33855BF8}" name="Part Number" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{EB01044E-239A-43EB-B0C2-1F87DDB54160}" name="Description" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{B7904B75-EB47-4AE0-AC16-835BCD406E73}" name="Added to Altium?" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{0881C807-AE0D-4E97-942D-F1BB4BC72740}" name="Name" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{FF11C1E0-268B-4AB9-A529-8334EF2C69FD}" name="# GPIO" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{55162BE7-C291-4B9F-ABE8-A7DE102A5A2F}" name="UART" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{12871EC5-67F1-442C-B9F6-E715FA2B13DA}" name="SPI" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{0676FDA2-81C4-49A9-A3D1-DEE7F28D8014}" name="I2C" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{4D86DECE-60FC-46A0-B57F-AB144D9C1459}" name="PWM" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{F498CA82-C855-4B59-BFFB-E076763E2C7B}" name="USB" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{1C8B55E3-7B48-484B-9DEC-D60D33855BF8}" name="Part Number" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{EB01044E-239A-43EB-B0C2-1F87DDB54160}" name="Description" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}" name="Resistors" displayName="Resistors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}" name="Resistors" displayName="Resistors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:H100" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H50">
     <sortCondition ref="C1:C50"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{5CCC4BAB-E9A7-42D2-BFCF-40A14E4FCFB3}" name="Added to Altium?" dataDxfId="76"/>
-    <tableColumn id="1" xr3:uid="{E2BB1AD3-36C9-4D80-8A78-E46D0D28B43D}" name="Resistance" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{C2F2285A-BFA3-4714-8945-6FE63C9CDE81}" name="Res (Raw)" dataDxfId="74">
+    <tableColumn id="8" xr3:uid="{5CCC4BAB-E9A7-42D2-BFCF-40A14E4FCFB3}" name="Added to Altium?" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{E2BB1AD3-36C9-4D80-8A78-E46D0D28B43D}" name="Resistance" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{C2F2285A-BFA3-4714-8945-6FE63C9CDE81}" name="Res (Raw)" dataDxfId="11">
       <calculatedColumnFormula>IF(ISNUMBER(B2),
 IF(B2=0,"",B2),
 VALUE(LEFT(B2,LEN(B2)-1))*
@@ -3340,11 +3400,11 @@
 IF(RIGHT(B2,1)="M",1000000,
 IF(RIGHT(B2,1)="m",0.001,1))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{67EED117-D01D-4FE8-BB40-D7D8F55BAB48}" name="Tolerance" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{F1269AFE-5CA5-4F00-93B8-6023E945504D}" name="Package" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{A4374340-1758-433F-80B6-83ABF6D97E11}" name="Wattage" dataDxfId="71"/>
-    <tableColumn id="5" xr3:uid="{7C53E4E9-C23D-4482-9A46-441AB8A4E1B1}" name="Part Number" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{BD8216A4-1B75-4738-A589-0D33231AD075}" name="Description" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{67EED117-D01D-4FE8-BB40-D7D8F55BAB48}" name="Tolerance" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{F1269AFE-5CA5-4F00-93B8-6023E945504D}" name="Package" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{A4374340-1758-433F-80B6-83ABF6D97E11}" name="Wattage" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{7C53E4E9-C23D-4482-9A46-441AB8A4E1B1}" name="Part Number" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{BD8216A4-1B75-4738-A589-0D33231AD075}" name="Description" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3422,20 +3482,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="74">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="63"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="73"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="70"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3458,13 +3518,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="65">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="64"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3484,8 +3544,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="62"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3495,11 +3555,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="61">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="59"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -3510,25 +3570,25 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="58">
   <autoFilter ref="A1:E11" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="47"/>
-    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="52">
   <autoFilter ref="A1:I10" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="50"/>
     <tableColumn id="4" xr3:uid="{D6AD8AA5-BC88-4F36-A647-B68EB5308316}" name="Automotive Fuse Size"/>
     <tableColumn id="1" xr3:uid="{5D9981C8-F221-4013-A9BA-4E5BF3474E5D}" name="Trip Current"/>
     <tableColumn id="2" xr3:uid="{494ED5E9-E1DA-4E76-9EAF-806837FCC14C}" name="Package"/>
@@ -3542,15 +3602,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="49">
   <autoFilter ref="A1:F11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="6">
-    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="38"/>
-    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4006,7 +4066,7 @@
         <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>213</v>
@@ -4057,16 +4117,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -4080,10 +4140,10 @@
         <v>213</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -4094,21 +4154,36 @@
         <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -4390,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="C11" t="s">
         <v>361</v>
@@ -4399,16 +4474,16 @@
         <v>103</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="H11" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -4416,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C12" t="s">
         <v>415</v>
@@ -4425,16 +4500,16 @@
         <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="F12" t="s">
         <v>360</v>
       </c>
       <c r="G12" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="H12" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -4728,10 +4803,10 @@
         <v>232</v>
       </c>
       <c r="C8" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="D8" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4742,10 +4817,10 @@
         <v>232</v>
       </c>
       <c r="C9" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="D9" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5244,10 +5319,10 @@
         <v>193</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -5271,10 +5346,10 @@
         <v>137</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -5903,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C31" s="17">
         <f t="shared" si="0"/>
@@ -5919,10 +5994,10 @@
         <v>193</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -5946,10 +6021,10 @@
         <v>193</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -5973,10 +6048,10 @@
         <v>193</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -5984,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C34" s="17">
         <f t="shared" ref="C34:C97" si="1">IF(ISNUMBER(B34),
@@ -6005,10 +6080,10 @@
         <v>193</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -6026,16 +6101,16 @@
         <v>62</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -6050,7 +6125,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>8</v>
@@ -6059,10 +6134,10 @@
         <v>193</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -6070,7 +6145,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="C37" s="17">
         <f t="shared" si="1"/>
@@ -6086,10 +6161,10 @@
         <v>193</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -6097,7 +6172,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="C38" s="17">
         <f t="shared" si="1"/>
@@ -6113,10 +6188,10 @@
         <v>193</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -6124,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="C39" s="17">
         <f t="shared" si="1"/>
@@ -6140,10 +6215,10 @@
         <v>193</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -6151,7 +6226,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="C40" s="17">
         <f t="shared" si="1"/>
@@ -6167,10 +6242,10 @@
         <v>193</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -6178,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="C41" s="17">
         <f t="shared" si="1"/>
@@ -6194,10 +6269,10 @@
         <v>193</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -6205,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="C42" s="17">
         <f t="shared" si="1"/>
@@ -6221,10 +6296,10 @@
         <v>193</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -6232,7 +6307,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="C43" s="17">
         <f t="shared" si="1"/>
@@ -6248,10 +6323,10 @@
         <v>137</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -6259,7 +6334,7 @@
         <v>1</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C44" s="17">
         <f t="shared" si="1"/>
@@ -6275,10 +6350,10 @@
         <v>193</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -6286,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="C45" s="17">
         <f t="shared" si="1"/>
@@ -6302,10 +6377,10 @@
         <v>193</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -6313,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="C46" s="17">
         <f t="shared" si="1"/>
@@ -6329,10 +6404,10 @@
         <v>193</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -6340,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="C47" s="17">
         <f t="shared" si="1"/>
@@ -6356,10 +6431,10 @@
         <v>193</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -6367,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="C48" s="17">
         <f t="shared" si="1"/>
@@ -6383,28 +6458,38 @@
         <v>193</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="B49" s="15">
-        <v>0</v>
-      </c>
-      <c r="C49" s="17" t="str">
+        <v>1</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>874</v>
+      </c>
+      <c r="C49" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
+        <v>158000</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>876</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="18" t="b">
@@ -7415,22 +7500,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="C6" t="s">
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="E6" t="s">
         <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="G6" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -7438,22 +7523,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="C7" t="s">
         <v>310</v>
       </c>
       <c r="D7" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="E7" t="s">
         <v>171</v>
       </c>
       <c r="F7" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="G7" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -7632,13 +7717,13 @@
         <v>295</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="G1" s="21" t="s">
         <v>297</v>
@@ -7690,19 +7775,19 @@
         <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="F3" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="G3" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="H3" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="I3" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -7716,22 +7801,22 @@
         <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="E4" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="F4" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="G4" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="H4" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="I4" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -7739,28 +7824,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C5" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="D5" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="E5" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="F5" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="G5" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="H5" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="I5" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -7771,25 +7856,25 @@
         <v>296</v>
       </c>
       <c r="C6" t="s">
+        <v>727</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>741</v>
-      </c>
       <c r="F6" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="G6" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="H6" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="I6" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -7806,19 +7891,19 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="F7" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="G7" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="H7" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="I7" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -7835,19 +7920,19 @@
         <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="F8" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="G8" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="H8" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="I8" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -7861,22 +7946,22 @@
         <v>298</v>
       </c>
       <c r="D9" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="E9" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="F9" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="G9" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="H9" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="I9" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -8113,7 +8198,7 @@
         <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -8704,7 +8789,7 @@
         <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="D23" t="s">
         <v>343</v>
@@ -8722,7 +8807,7 @@
         <v>112</v>
       </c>
       <c r="I23" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -8730,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>23</v>
@@ -8751,7 +8836,7 @@
         <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -8780,7 +8865,7 @@
         <v>9</v>
       </c>
       <c r="I25" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -8788,7 +8873,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
@@ -8809,7 +8894,7 @@
         <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -8817,10 +8902,10 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="D27" t="s">
         <v>343</v>
@@ -8838,7 +8923,7 @@
         <v>112</v>
       </c>
       <c r="I27" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -8846,7 +8931,7 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>8</v>
@@ -8867,7 +8952,7 @@
         <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -8896,7 +8981,7 @@
         <v>112</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -8904,7 +8989,7 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>8</v>
@@ -8925,7 +9010,7 @@
         <v>9</v>
       </c>
       <c r="I30" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -8933,7 +9018,7 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>8</v>
@@ -8954,7 +9039,7 @@
         <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -8965,7 +9050,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="D32" t="s">
         <v>106</v>
@@ -8983,7 +9068,7 @@
         <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
@@ -9176,7 +9261,7 @@
         <v>125</v>
       </c>
       <c r="H3" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="I3" t="s">
         <v>366</v>
@@ -9225,22 +9310,22 @@
         <v>363</v>
       </c>
       <c r="D5" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="E5" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="F5" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="G5" t="s">
         <v>103</v>
       </c>
       <c r="I5" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="J5" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -9254,22 +9339,22 @@
         <v>363</v>
       </c>
       <c r="D6" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="G6" t="s">
         <v>103</v>
       </c>
       <c r="I6" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="J6" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -9283,7 +9368,7 @@
         <v>363</v>
       </c>
       <c r="D7" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -9295,10 +9380,10 @@
         <v>103</v>
       </c>
       <c r="I7" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="J7" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -9324,7 +9409,7 @@
         <v>103</v>
       </c>
       <c r="H8" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="I8" t="s">
         <v>145</v>
@@ -9344,10 +9429,10 @@
         <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="E9" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F9" t="s">
         <v>392</v>
@@ -9356,10 +9441,10 @@
         <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="J9" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -9373,10 +9458,10 @@
         <v>224</v>
       </c>
       <c r="D10" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="E10" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="F10" t="s">
         <v>119</v>
@@ -9385,10 +9470,10 @@
         <v>103</v>
       </c>
       <c r="I10" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="J10" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -9402,30 +9487,30 @@
         <v>224</v>
       </c>
       <c r="D11" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="E11" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="F11" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="G11" t="s">
         <v>103</v>
       </c>
       <c r="H11" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="I11" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="J11" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
         <v>143</v>
@@ -9434,10 +9519,10 @@
         <v>224</v>
       </c>
       <c r="D12" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="E12" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="F12" t="s">
         <v>119</v>
@@ -9446,13 +9531,13 @@
         <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="I12" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="J12" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -9828,7 +9913,7 @@
         <v>331</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -10138,16 +10223,16 @@
         <v>331</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -10155,7 +10240,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C30" s="12">
         <v>3</v>
@@ -10164,16 +10249,16 @@
         <v>331</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -10181,7 +10266,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C31" s="12">
         <v>2</v>
@@ -10190,16 +10275,16 @@
         <v>331</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -10207,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C32" s="12">
         <v>10</v>
@@ -10227,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C33" s="12">
         <v>16</v>
@@ -10410,13 +10495,13 @@
         <v>331</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>410</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -10456,13 +10541,13 @@
         <v>331</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -10479,13 +10564,13 @@
         <v>331</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -10612,16 +10697,16 @@
         <v>330</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>475</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -10629,7 +10714,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="C52" s="12">
         <v>1</v>
@@ -10638,13 +10723,13 @@
         <v>331</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -10661,13 +10746,13 @@
         <v>330</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -10684,13 +10769,13 @@
         <v>330</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -10698,25 +10783,25 @@
         <v>1</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="C55" s="12">
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -10724,7 +10809,7 @@
         <v>1</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="C56" s="12">
         <v>1</v>
@@ -10733,29 +10818,69 @@
         <v>202</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C57" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="C57" s="12">
+        <v>4</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>868</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C58" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="C58" s="12">
+        <v>4</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>868</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="b">
@@ -11108,27 +11233,45 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C4" t="s">
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E4" t="s">
         <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="G4" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>883</v>
+      </c>
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" t="s">
+        <v>884</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="s">
+        <v>885</v>
+      </c>
+      <c r="G5" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -11225,7 +11368,7 @@
         <v>114</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>115</v>
@@ -11251,7 +11394,7 @@
         <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="F2" t="s">
         <v>172</v>
@@ -11277,7 +11420,7 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="F3" t="s">
         <v>120</v>
@@ -11300,7 +11443,7 @@
         <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="F4" t="s">
         <v>464</v>
@@ -11320,22 +11463,22 @@
         <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D5" t="s">
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="F5" t="s">
         <v>469</v>
       </c>
       <c r="G5" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="H5" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -11349,7 +11492,7 @@
         <v>524</v>
       </c>
       <c r="E6" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="F6" t="s">
         <v>172</v>
@@ -11369,19 +11512,19 @@
         <v>523</v>
       </c>
       <c r="C7" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="E7" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="F7" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="G7" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="H7" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -11395,7 +11538,7 @@
         <v>468</v>
       </c>
       <c r="E8" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F8" t="s">
         <v>469</v>
@@ -11424,10 +11567,10 @@
         <v>464</v>
       </c>
       <c r="G9" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="H9" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -11438,19 +11581,19 @@
         <v>467</v>
       </c>
       <c r="C10" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="E10" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F10" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="G10" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="H10" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -11461,19 +11604,19 @@
         <v>467</v>
       </c>
       <c r="C11" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="E11" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F11" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="G11" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="H11" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11484,19 +11627,19 @@
         <v>523</v>
       </c>
       <c r="C12" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="E12" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F12" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="G12" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="H12" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -11510,16 +11653,16 @@
         <v>524</v>
       </c>
       <c r="E13" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F13" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="G13" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="H13" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -11600,16 +11743,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C2" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="D2" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E2" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -11617,16 +11760,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C3" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="D3" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="E3" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -11651,13 +11794,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D5" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="E5" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -11682,16 +11825,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="C7" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="D7" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E7" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -11713,16 +11856,16 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C9" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="D9" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="E9" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -11730,16 +11873,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>540</v>
-      </c>
-      <c r="C10" t="s">
-        <v>541</v>
+        <v>882</v>
       </c>
       <c r="D10" t="s">
-        <v>542</v>
+        <v>880</v>
       </c>
       <c r="E10" t="s">
-        <v>543</v>
+        <v>881</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -11761,16 +11901,16 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E12" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -11778,16 +11918,16 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="C13" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="D13" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="E13" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -11795,16 +11935,16 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="C14" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="D14" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="E14" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -11812,16 +11952,16 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="C15" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="D15" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E15" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -11829,16 +11969,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="C16" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="D16" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="E16" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -11846,13 +11986,13 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="D17" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E17" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -11860,16 +12000,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="C18" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="D18" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="E18" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -11911,16 +12051,16 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="C21" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="D21" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="E21" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -11993,16 +12133,16 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
+        <v>879</v>
+      </c>
+      <c r="C26" t="s">
         <v>536</v>
       </c>
-      <c r="C26" t="s">
-        <v>538</v>
-      </c>
       <c r="D26" t="s">
-        <v>537</v>
+        <v>877</v>
       </c>
       <c r="E26" t="s">
-        <v>539</v>
+        <v>878</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -12044,13 +12184,13 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="D29" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="E29" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -12058,16 +12198,16 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C30" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="D30" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="E30" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -12075,16 +12215,16 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C31" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="D31" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="E31" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -12092,16 +12232,16 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="C32" t="s">
         <v>218</v>
       </c>
       <c r="D32" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="E32" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -12109,16 +12249,16 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C33" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="D33" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="E33" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -12234,7 +12374,7 @@
         <v>197</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>243</v>
+        <v>888</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>246</v>
@@ -12359,16 +12499,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="C8" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="D8" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="F8" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12376,13 +12516,13 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="C9" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="D9" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12390,21 +12530,36 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="C10" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="D10" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="E10" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>889</v>
+      </c>
+      <c r="C11" t="s">
+        <v>887</v>
+      </c>
+      <c r="D11" t="s">
+        <v>890</v>
+      </c>
+      <c r="E11" t="s">
+        <v>887</v>
+      </c>
+      <c r="F11" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB77531-BB17-43DB-8EB8-BF3D267EFD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D612E23B-E267-4084-936D-D6440F7D8B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="6" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="6" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome!" sheetId="15" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="901">
   <si>
     <t>Capacitance</t>
   </si>
@@ -2735,6 +2735,33 @@
   </si>
   <si>
     <t>https://www.winson.com.tw/uploads/images/WCS1600.pdf</t>
+  </si>
+  <si>
+    <t>Bridge (UART-RS485)</t>
+  </si>
+  <si>
+    <t>THVD1400DR</t>
+  </si>
+  <si>
+    <t>1/1 Transceiver Half RS422, RS485 8-SOIC</t>
+  </si>
+  <si>
+    <t>7,12V</t>
+  </si>
+  <si>
+    <t>400W</t>
+  </si>
+  <si>
+    <t>CDSOT23-SM712</t>
+  </si>
+  <si>
+    <t>26V, 14V Clamp 17A (8/20µs) Ipp Tvs Diode Surface Mount SOT-23-3</t>
+  </si>
+  <si>
+    <t>Tube</t>
+  </si>
+  <si>
+    <t>2mL Tube</t>
   </si>
 </sst>
 </file>
@@ -3151,23 +3178,6 @@
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
@@ -3237,6 +3247,23 @@
         </ext>
       </extLst>
     </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3281,13 +3308,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
   <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="78"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="75"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="74"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="76"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="72"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3482,20 +3509,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="71">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="73"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="68"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="66"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="65"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3518,13 +3545,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="62">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="61"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3544,8 +3571,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="59"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3555,11 +3582,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="78">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="77"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="76"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -11667,7 +11694,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>523</v>
+      </c>
+      <c r="C14" t="s">
+        <v>895</v>
+      </c>
+      <c r="E14" t="s">
+        <v>896</v>
+      </c>
+      <c r="F14" t="s">
+        <v>846</v>
+      </c>
+      <c r="G14" t="s">
+        <v>897</v>
+      </c>
+      <c r="H14" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -12263,7 +12308,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>892</v>
+      </c>
+      <c r="D34" t="s">
+        <v>893</v>
+      </c>
+      <c r="E34" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -12564,7 +12618,19 @@
     </row>
     <row r="12" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>899</v>
+      </c>
+      <c r="C12" t="s">
+        <v>900</v>
+      </c>
+      <c r="D12" t="s">
+        <v>900</v>
+      </c>
+      <c r="E12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D612E23B-E267-4084-936D-D6440F7D8B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928560F9-6FBA-494F-AFA4-D90DD79CAD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="6" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="10" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome!" sheetId="15" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="922">
   <si>
     <t>Capacitance</t>
   </si>
@@ -2762,6 +2762,69 @@
   </si>
   <si>
     <t>2mL Tube</t>
+  </si>
+  <si>
+    <t>0353620650</t>
+  </si>
+  <si>
+    <t>0355070600</t>
+  </si>
+  <si>
+    <t>6 Position Rectangular Housing Connector Receptacle Natural 0.079" (2.00mm)</t>
+  </si>
+  <si>
+    <t>TLC5916IPW</t>
+  </si>
+  <si>
+    <t>Shift Register</t>
+  </si>
+  <si>
+    <t>8-bit shift register for common anode LEDs</t>
+  </si>
+  <si>
+    <t>LED Driver IC 8 Output Linear Shift Register Dimming 120mA 16-TSSOP</t>
+  </si>
+  <si>
+    <t>Seven-Seg Display</t>
+  </si>
+  <si>
+    <t>Millicandela</t>
+  </si>
+  <si>
+    <t>19.00mm x 12.50mm x 3.25mm</t>
+  </si>
+  <si>
+    <t>600mcd</t>
+  </si>
+  <si>
+    <t>DSM7TA56105T</t>
+  </si>
+  <si>
+    <t>Display Modules - LED Character and Numeric Green 7-Segment 1 Character Common Anode 3.1V 20mA 0.748" H x 0.492" W x 0.128" D (19.00mm x 12.50mm x 3.25mm) 10-SMD, No Lead</t>
+  </si>
+  <si>
+    <t>26.05mcd</t>
+  </si>
+  <si>
+    <t>162.5mcd</t>
+  </si>
+  <si>
+    <t>104mcd</t>
+  </si>
+  <si>
+    <t>145mcd</t>
+  </si>
+  <si>
+    <t>30mcd</t>
+  </si>
+  <si>
+    <t>35mcd</t>
+  </si>
+  <si>
+    <t>3800mcd</t>
+  </si>
+  <si>
+    <t>72.5mcd Red, 435mcd Green, 105mcd Blue</t>
   </si>
 </sst>
 </file>
@@ -3178,6 +3241,23 @@
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
@@ -3198,6 +3278,22 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3230,39 +3326,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3308,13 +3371,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
   <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="69"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="68"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="66"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3323,15 +3386,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:H20" totalsRowShown="0">
-  <autoFilter ref="A1:H20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:I20" totalsRowShown="0">
+  <autoFilter ref="A1:I20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
+  <tableColumns count="9">
     <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="42"/>
     <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="41"/>
     <tableColumn id="1" xr3:uid="{727DF6C0-6BC9-4CBC-ACBD-F7D7801F3DED}" name="Color"/>
     <tableColumn id="6" xr3:uid="{2F89F121-2031-4E76-8B64-C6BE1AC4E5A7}" name="Mount Type"/>
     <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="40"/>
     <tableColumn id="3" xr3:uid="{95A3DF17-FA71-419C-9869-87ACAC774187}" name="Dome"/>
+    <tableColumn id="9" xr3:uid="{51A8C34B-CA0A-4A26-89E6-8BD3AFCDABB1}" name="Millicandela"/>
     <tableColumn id="4" xr3:uid="{30ACC022-FAF3-44FA-97E2-DA5C989B54D7}" name="Part Number"/>
     <tableColumn id="5" xr3:uid="{BDED051F-FA40-461B-85BB-40EDC316E70C}" name="Description"/>
   </tableColumns>
@@ -3509,20 +3573,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="78">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="70"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="66"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="65"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="77"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="73"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="72"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3545,13 +3609,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="65">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="64"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3571,8 +3635,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="62"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3582,11 +3646,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="61">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="77"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="59"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -4238,7 +4302,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9362198B-44BD-4E55-B62E-439143EC0CFE}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -4246,12 +4310,13 @@
     <col min="4" max="4" width="16.36328125" customWidth="1"/>
     <col min="5" max="5" width="14.36328125" style="3" customWidth="1"/>
     <col min="6" max="6" width="17.453125" customWidth="1"/>
-    <col min="7" max="7" width="31.81640625" customWidth="1"/>
-    <col min="8" max="8" width="43.26953125" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" hidden="1"/>
+    <col min="7" max="7" width="15.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.81640625" customWidth="1"/>
+    <col min="9" max="9" width="43.26953125" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>197</v>
       </c>
@@ -4271,13 +4336,16 @@
         <v>20</v>
       </c>
       <c r="G1" t="s">
+        <v>909</v>
+      </c>
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="b">
         <v>1</v>
       </c>
@@ -4297,10 +4365,13 @@
         <v>21</v>
       </c>
       <c r="G2" t="s">
+        <v>914</v>
+      </c>
+      <c r="H2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="b">
         <v>1</v>
       </c>
@@ -4320,10 +4391,13 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
+        <v>915</v>
+      </c>
+      <c r="H3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="b">
         <v>1</v>
       </c>
@@ -4343,10 +4417,13 @@
         <v>21</v>
       </c>
       <c r="G4" t="s">
+        <v>916</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="b">
         <v>1</v>
       </c>
@@ -4366,10 +4443,13 @@
         <v>21</v>
       </c>
       <c r="G5" t="s">
+        <v>917</v>
+      </c>
+      <c r="H5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="b">
         <v>1</v>
       </c>
@@ -4389,10 +4469,13 @@
         <v>21</v>
       </c>
       <c r="G6" t="s">
+        <v>918</v>
+      </c>
+      <c r="H6" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="b">
         <v>1</v>
       </c>
@@ -4411,14 +4494,14 @@
       <c r="F7" t="s">
         <v>360</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>16347</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="b">
         <v>1</v>
       </c>
@@ -4438,10 +4521,13 @@
         <v>21</v>
       </c>
       <c r="G8" t="s">
+        <v>919</v>
+      </c>
+      <c r="H8" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="b">
         <v>1</v>
       </c>
@@ -4461,10 +4547,13 @@
         <v>21</v>
       </c>
       <c r="G9" t="s">
+        <v>920</v>
+      </c>
+      <c r="H9" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="b">
         <v>1</v>
       </c>
@@ -4484,10 +4573,13 @@
         <v>21</v>
       </c>
       <c r="G10" t="s">
+        <v>918</v>
+      </c>
+      <c r="H10" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="b">
         <v>1</v>
       </c>
@@ -4507,13 +4599,16 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
+        <v>921</v>
+      </c>
+      <c r="H11" t="s">
         <v>593</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="b">
         <v>1</v>
       </c>
@@ -4532,29 +4627,53 @@
       <c r="F12" t="s">
         <v>360</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>710</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>908</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>911</v>
+      </c>
+      <c r="H13" t="s">
+        <v>912</v>
+      </c>
+      <c r="I13" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="b">
         <v>0</v>
       </c>
@@ -9908,22 +10027,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>511</v>
+        <v>204</v>
       </c>
       <c r="C14" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>512</v>
+        <v>716</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>514</v>
+        <v>647</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>513</v>
+        <v>717</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -9931,16 +10050,22 @@
         <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>511</v>
+        <v>204</v>
       </c>
       <c r="C15" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>820</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>549</v>
+        <v>821</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -9948,19 +10073,22 @@
         <v>1</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="C16" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>496</v>
+        <v>512</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>514</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -9968,19 +10096,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="C17" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>499</v>
+        <v>331</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -9988,25 +10113,19 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>443</v>
+        <v>495</v>
       </c>
       <c r="C18" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>447</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -10014,25 +10133,19 @@
         <v>1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>443</v>
+        <v>495</v>
       </c>
       <c r="C19" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>330</v>
+        <v>202</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>448</v>
+        <v>498</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>446</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -10043,16 +10156,22 @@
         <v>443</v>
       </c>
       <c r="C20" s="12">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>461</v>
+        <v>449</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -10063,19 +10182,22 @@
         <v>443</v>
       </c>
       <c r="C21" s="12">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>330</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>463</v>
+        <v>448</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -10086,19 +10208,16 @@
         <v>443</v>
       </c>
       <c r="C22" s="12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -10109,45 +10228,42 @@
         <v>443</v>
       </c>
       <c r="C23" s="12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>330</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>477</v>
-      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>443</v>
       </c>
       <c r="C24" s="12">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>39</v>
+        <v>475</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>157</v>
+        <v>476</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>40</v>
+        <v>478</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -10155,22 +10271,25 @@
         <v>1</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>443</v>
       </c>
       <c r="C25" s="12">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>476</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>175</v>
+        <v>475</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>463</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>37</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -10178,19 +10297,25 @@
         <v>1</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>443</v>
       </c>
       <c r="C26" s="12">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>207</v>
+        <v>679</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>206</v>
+        <v>475</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -10201,16 +10326,19 @@
         <v>152</v>
       </c>
       <c r="C27" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -10218,22 +10346,22 @@
         <v>1</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="C28" s="12">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -10241,25 +10369,19 @@
         <v>1</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="C29" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>645</v>
+        <v>207</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>648</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -10267,25 +10389,19 @@
         <v>1</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>633</v>
+        <v>152</v>
       </c>
       <c r="C30" s="12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>635</v>
+        <v>41</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>637</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -10293,25 +10409,22 @@
         <v>1</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>633</v>
+        <v>205</v>
       </c>
       <c r="C31" s="12">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>642</v>
+        <v>165</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>635</v>
+        <v>165</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>644</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -10319,19 +10432,25 @@
         <v>1</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>649</v>
+        <v>205</v>
       </c>
       <c r="C32" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>36</v>
+        <v>645</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>647</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>35</v>
+        <v>648</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -10339,16 +10458,25 @@
         <v>1</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C33" s="12">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>442</v>
+        <v>634</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -10356,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>150</v>
+        <v>633</v>
       </c>
       <c r="C34" s="12">
         <v>2</v>
@@ -10365,10 +10493,16 @@
         <v>331</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>148</v>
+        <v>642</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>635</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>95</v>
+        <v>644</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -10376,19 +10510,25 @@
         <v>1</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>150</v>
+        <v>865</v>
       </c>
       <c r="C35" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>94</v>
+        <v>866</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>867</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>95</v>
+        <v>868</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -10396,19 +10536,25 @@
         <v>1</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>150</v>
+        <v>865</v>
       </c>
       <c r="C36" s="12">
         <v>4</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>347</v>
+        <v>866</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>867</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>348</v>
+        <v>868</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -10416,19 +10562,19 @@
         <v>1</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>150</v>
+        <v>649</v>
       </c>
       <c r="C37" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>345</v>
+        <v>36</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>346</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -10436,19 +10582,16 @@
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>150</v>
+        <v>649</v>
       </c>
       <c r="C38" s="12">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>350</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -10459,11 +10602,17 @@
         <v>150</v>
       </c>
       <c r="C39" s="12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>331</v>
       </c>
+      <c r="E39" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="b">
@@ -10473,16 +10622,16 @@
         <v>150</v>
       </c>
       <c r="C40" s="12">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>351</v>
+        <v>94</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>352</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -10490,22 +10639,19 @@
         <v>1</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="C41" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>410</v>
+        <v>347</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>409</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -10513,22 +10659,19 @@
         <v>1</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="C42" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>410</v>
+        <v>345</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>544</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -10536,22 +10679,19 @@
         <v>1</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="C43" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>410</v>
+        <v>349</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>418</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -10559,45 +10699,33 @@
         <v>1</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="C44" s="12">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>570</v>
-      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>408</v>
+        <v>150</v>
       </c>
       <c r="C45" s="12">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>678</v>
+        <v>351</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>677</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -10605,22 +10733,22 @@
         <v>1</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>329</v>
+        <v>408</v>
       </c>
       <c r="C46" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>332</v>
+        <v>407</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>333</v>
+        <v>410</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>334</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -10628,22 +10756,22 @@
         <v>1</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>335</v>
+        <v>408</v>
       </c>
       <c r="C47" s="12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>401</v>
+        <v>543</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>333</v>
+        <v>410</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>402</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -10651,7 +10779,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>265</v>
+        <v>408</v>
       </c>
       <c r="C48" s="12">
         <v>4</v>
@@ -10660,13 +10788,13 @@
         <v>331</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>266</v>
+        <v>417</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>333</v>
+        <v>410</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>267</v>
+        <v>418</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -10674,19 +10802,22 @@
         <v>1</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>479</v>
+        <v>408</v>
       </c>
       <c r="C49" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>480</v>
+        <v>568</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>481</v>
+        <v>570</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -10694,20 +10825,22 @@
         <v>1</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C50" s="12"/>
+        <v>408</v>
+      </c>
+      <c r="C50" s="12">
+        <v>2</v>
+      </c>
       <c r="D50" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>92</v>
+        <v>676</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>242</v>
+        <v>678</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>93</v>
+        <v>677</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -10715,25 +10848,22 @@
         <v>1</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>443</v>
+        <v>704</v>
       </c>
       <c r="C51" s="12">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>475</v>
+        <v>705</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>680</v>
+        <v>706</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>681</v>
+        <v>707</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -10741,22 +10871,25 @@
         <v>1</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>704</v>
+        <v>861</v>
       </c>
       <c r="C52" s="12">
         <v>1</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>705</v>
+        <v>862</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>706</v>
+        <v>863</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>707</v>
+        <v>864</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -10764,22 +10897,25 @@
         <v>1</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>204</v>
+        <v>834</v>
       </c>
       <c r="C53" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>330</v>
+        <v>835</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>716</v>
+        <v>836</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>837</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>647</v>
+        <v>838</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>717</v>
+        <v>839</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -10787,22 +10923,22 @@
         <v>1</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>204</v>
+        <v>329</v>
       </c>
       <c r="C54" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>820</v>
+        <v>332</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>821</v>
+        <v>333</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>822</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -10810,25 +10946,22 @@
         <v>1</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>834</v>
+        <v>335</v>
       </c>
       <c r="C55" s="12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>835</v>
+        <v>331</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>837</v>
+        <v>401</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>838</v>
+        <v>333</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>839</v>
+        <v>402</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -10836,25 +10969,22 @@
         <v>1</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>861</v>
+        <v>265</v>
       </c>
       <c r="C56" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>863</v>
+        <v>333</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>864</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -10862,25 +10992,19 @@
         <v>1</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>865</v>
+        <v>479</v>
       </c>
       <c r="C57" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>867</v>
+        <v>480</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>868</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -10888,32 +11012,47 @@
         <v>1</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="C58" s="12">
-        <v>4</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C58" s="12"/>
       <c r="D58" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>866</v>
+        <v>92</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>867</v>
+        <v>242</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>868</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C59" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C59" s="12">
+        <v>6</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>903</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="b">
@@ -12322,7 +12461,19 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>905</v>
+      </c>
+      <c r="C35" t="s">
+        <v>906</v>
+      </c>
+      <c r="D35" t="s">
+        <v>904</v>
+      </c>
+      <c r="E35" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928560F9-6FBA-494F-AFA4-D90DD79CAD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410A7766-C58E-40F3-BAEC-3D422FA03C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="10" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="5" activeTab="5" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome!" sheetId="15" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="932">
   <si>
     <t>Capacitance</t>
   </si>
@@ -1414,15 +1414,9 @@
     <t>1kbit</t>
   </si>
   <si>
-    <t>128 x 8/64 x 16</t>
-  </si>
-  <si>
     <t>3-Wire</t>
   </si>
   <si>
-    <t>FLASH</t>
-  </si>
-  <si>
     <t>M93C46-WMN6TP</t>
   </si>
   <si>
@@ -2825,6 +2819,42 @@
   </si>
   <si>
     <t>72.5mcd Red, 435mcd Green, 105mcd Blue</t>
+  </si>
+  <si>
+    <t>USB-B Vertical</t>
+  </si>
+  <si>
+    <t>USB-B-S-VT</t>
+  </si>
+  <si>
+    <t>USB-B (USB TYPE-B) USB 2.0 Receptacle Connector 4 Position Through Hole</t>
+  </si>
+  <si>
+    <t>16kbit</t>
+  </si>
+  <si>
+    <t>M93C86-WMN6TP</t>
+  </si>
+  <si>
+    <t>EEPROM Memory IC 16Kbit Microwire 2 MHz 8-SOIC</t>
+  </si>
+  <si>
+    <t>EEPROM</t>
+  </si>
+  <si>
+    <t>2048 x 8 / 1024 x 16</t>
+  </si>
+  <si>
+    <t>128 x 8 / 64 x 16</t>
+  </si>
+  <si>
+    <t>Single Tri-State Output, Active-High OE</t>
+  </si>
+  <si>
+    <t>SN74LVC1G126DCKR</t>
+  </si>
+  <si>
+    <t>Buffer, Non-Inverting 1 Element 1 Bit per Element 3-State Output SC-70-5</t>
   </si>
 </sst>
 </file>
@@ -3159,23 +3189,6 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -3289,22 +3302,6 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -3326,6 +3323,39 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3371,13 +3401,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
   <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="75"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="74"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="72"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3389,11 +3419,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:I20" totalsRowShown="0">
   <autoFilter ref="A1:I20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="78"/>
+    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="77"/>
     <tableColumn id="1" xr3:uid="{727DF6C0-6BC9-4CBC-ACBD-F7D7801F3DED}" name="Color"/>
     <tableColumn id="6" xr3:uid="{2F89F121-2031-4E76-8B64-C6BE1AC4E5A7}" name="Mount Type"/>
-    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="76"/>
     <tableColumn id="3" xr3:uid="{95A3DF17-FA71-419C-9869-87ACAC774187}" name="Dome"/>
     <tableColumn id="9" xr3:uid="{51A8C34B-CA0A-4A26-89E6-8BD3AFCDABB1}" name="Millicandela"/>
     <tableColumn id="4" xr3:uid="{30ACC022-FAF3-44FA-97E2-DA5C989B54D7}" name="Part Number"/>
@@ -3573,20 +3603,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="71">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="77"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="71"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="66"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="65"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3609,13 +3639,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="62">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="61"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3635,8 +3665,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="59"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3646,11 +3676,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="58">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="56"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -3661,25 +3691,25 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="55">
   <autoFilter ref="A1:E11" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="57"/>
-    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="49">
   <autoFilter ref="A1:I10" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="47"/>
     <tableColumn id="4" xr3:uid="{D6AD8AA5-BC88-4F36-A647-B68EB5308316}" name="Automotive Fuse Size"/>
     <tableColumn id="1" xr3:uid="{5D9981C8-F221-4013-A9BA-4E5BF3474E5D}" name="Trip Current"/>
     <tableColumn id="2" xr3:uid="{494ED5E9-E1DA-4E76-9EAF-806837FCC14C}" name="Package"/>
@@ -3693,15 +3723,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="46">
   <autoFilter ref="A1:F11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="6">
-    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="48"/>
-    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4157,7 +4187,7 @@
         <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>213</v>
@@ -4208,16 +4238,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>656</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -4231,10 +4261,10 @@
         <v>213</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -4245,16 +4275,16 @@
         <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>847</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>848</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -4262,19 +4292,19 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>870</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -4336,7 +4366,7 @@
         <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
@@ -4365,7 +4395,7 @@
         <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="H2" t="s">
         <v>22</v>
@@ -4391,7 +4421,7 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -4417,7 +4447,7 @@
         <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H4" t="s">
         <v>27</v>
@@ -4443,7 +4473,7 @@
         <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="H5" t="s">
         <v>28</v>
@@ -4469,7 +4499,7 @@
         <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H6" t="s">
         <v>354</v>
@@ -4521,7 +4551,7 @@
         <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H8" t="s">
         <v>411</v>
@@ -4547,7 +4577,7 @@
         <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="H9" t="s">
         <v>416</v>
@@ -4573,7 +4603,7 @@
         <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H10" t="s">
         <v>432</v>
@@ -4584,7 +4614,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C11" t="s">
         <v>361</v>
@@ -4593,19 +4623,19 @@
         <v>103</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I11" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -4613,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C12" t="s">
         <v>415</v>
@@ -4622,16 +4652,16 @@
         <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F12" t="s">
         <v>360</v>
       </c>
       <c r="H12" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="I12" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -4639,7 +4669,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -4648,19 +4678,19 @@
         <v>103</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
       </c>
       <c r="G13" t="s">
+        <v>909</v>
+      </c>
+      <c r="H13" t="s">
+        <v>910</v>
+      </c>
+      <c r="I13" t="s">
         <v>911</v>
-      </c>
-      <c r="H13" t="s">
-        <v>912</v>
-      </c>
-      <c r="I13" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -4769,27 +4799,45 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>451</v>
+        <v>928</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>450</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="F3" t="s">
         <v>452</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" t="s">
         <v>453</v>
-      </c>
-      <c r="F3" t="s">
-        <v>454</v>
-      </c>
-      <c r="G3" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>927</v>
+      </c>
+      <c r="C4" t="s">
+        <v>923</v>
+      </c>
+      <c r="D4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E4" t="s">
+        <v>926</v>
+      </c>
+      <c r="F4" t="s">
+        <v>924</v>
+      </c>
+      <c r="G4" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -4932,13 +4980,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>498</v>
+      </c>
+      <c r="C7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" t="s">
         <v>500</v>
-      </c>
-      <c r="C7" t="s">
-        <v>501</v>
-      </c>
-      <c r="D7" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -4949,10 +4997,10 @@
         <v>232</v>
       </c>
       <c r="C8" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D8" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4963,10 +5011,10 @@
         <v>232</v>
       </c>
       <c r="C9" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5023,16 +5071,16 @@
         <v>80</v>
       </c>
       <c r="D1" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>484</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F1" s="23" t="s">
         <v>486</v>
       </c>
-      <c r="F1" s="23" t="s">
-        <v>488</v>
-      </c>
       <c r="G1" s="23" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>31</v>
@@ -5049,19 +5097,19 @@
         <v>258</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>487</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -5069,25 +5117,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>485</v>
-      </c>
       <c r="E3" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -5465,10 +5513,10 @@
         <v>193</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -5492,10 +5540,10 @@
         <v>137</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -5638,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C13" s="17">
         <f t="shared" si="0"/>
@@ -5654,10 +5702,10 @@
         <v>193</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -5719,7 +5767,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C16" s="17">
         <f t="shared" si="0"/>
@@ -5735,10 +5783,10 @@
         <v>193</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -5773,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C18" s="17">
         <f t="shared" si="0"/>
@@ -5789,10 +5837,10 @@
         <v>193</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -5935,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C24" s="17">
         <f t="shared" si="0"/>
@@ -5951,10 +5999,10 @@
         <v>193</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -6124,7 +6172,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C31" s="17">
         <f t="shared" si="0"/>
@@ -6140,10 +6188,10 @@
         <v>193</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -6167,10 +6215,10 @@
         <v>193</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -6194,10 +6242,10 @@
         <v>193</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -6205,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C34" s="17">
         <f t="shared" ref="C34:C97" si="1">IF(ISNUMBER(B34),
@@ -6226,10 +6274,10 @@
         <v>193</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -6247,16 +6295,16 @@
         <v>62</v>
       </c>
       <c r="E35" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>612</v>
+      </c>
+      <c r="H35" s="16" t="s">
         <v>613</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>610</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>614</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -6271,7 +6319,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>8</v>
@@ -6280,10 +6328,10 @@
         <v>193</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -6291,7 +6339,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C37" s="17">
         <f t="shared" si="1"/>
@@ -6307,10 +6355,10 @@
         <v>193</v>
       </c>
       <c r="G37" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="H37" s="16" t="s">
         <v>772</v>
-      </c>
-      <c r="H37" s="16" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -6318,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C38" s="17">
         <f t="shared" si="1"/>
@@ -6334,10 +6382,10 @@
         <v>193</v>
       </c>
       <c r="G38" s="16" t="s">
+        <v>773</v>
+      </c>
+      <c r="H38" s="16" t="s">
         <v>775</v>
-      </c>
-      <c r="H38" s="16" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -6345,7 +6393,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C39" s="17">
         <f t="shared" si="1"/>
@@ -6361,10 +6409,10 @@
         <v>193</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -6372,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C40" s="17">
         <f t="shared" si="1"/>
@@ -6388,10 +6436,10 @@
         <v>193</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -6399,7 +6447,7 @@
         <v>1</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C41" s="17">
         <f t="shared" si="1"/>
@@ -6415,10 +6463,10 @@
         <v>193</v>
       </c>
       <c r="G41" s="16" t="s">
+        <v>782</v>
+      </c>
+      <c r="H41" s="16" t="s">
         <v>784</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -6426,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C42" s="17">
         <f t="shared" si="1"/>
@@ -6442,10 +6490,10 @@
         <v>193</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -6453,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C43" s="17">
         <f t="shared" si="1"/>
@@ -6469,10 +6517,10 @@
         <v>137</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -6480,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C44" s="17">
         <f t="shared" si="1"/>
@@ -6496,10 +6544,10 @@
         <v>193</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -6507,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C45" s="17">
         <f t="shared" si="1"/>
@@ -6523,10 +6571,10 @@
         <v>193</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -6534,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C46" s="17">
         <f t="shared" si="1"/>
@@ -6550,10 +6598,10 @@
         <v>193</v>
       </c>
       <c r="G46" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="H46" s="16" t="s">
         <v>799</v>
-      </c>
-      <c r="H46" s="16" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -6561,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C47" s="17">
         <f t="shared" si="1"/>
@@ -6577,10 +6625,10 @@
         <v>193</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -6588,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C48" s="17">
         <f t="shared" si="1"/>
@@ -6604,10 +6652,10 @@
         <v>193</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -6615,7 +6663,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C49" s="17">
         <f t="shared" si="1"/>
@@ -6631,10 +6679,10 @@
         <v>193</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -7646,22 +7694,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C6" t="s">
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E6" t="s">
         <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -7669,22 +7717,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C7" t="s">
         <v>310</v>
       </c>
       <c r="D7" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E7" t="s">
         <v>171</v>
       </c>
       <c r="F7" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G7" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -7863,13 +7911,13 @@
         <v>295</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G1" s="21" t="s">
         <v>297</v>
@@ -7921,19 +7969,19 @@
         <v>117</v>
       </c>
       <c r="E3" t="s">
+        <v>573</v>
+      </c>
+      <c r="F3" t="s">
         <v>575</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H3" t="s">
         <v>577</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>578</v>
-      </c>
-      <c r="H3" t="s">
-        <v>579</v>
-      </c>
-      <c r="I3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -7947,22 +7995,22 @@
         <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E4" t="s">
+        <v>582</v>
+      </c>
+      <c r="F4" t="s">
+        <v>583</v>
+      </c>
+      <c r="G4" t="s">
+        <v>581</v>
+      </c>
+      <c r="H4" t="s">
         <v>584</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>585</v>
-      </c>
-      <c r="G4" t="s">
-        <v>583</v>
-      </c>
-      <c r="H4" t="s">
-        <v>586</v>
-      </c>
-      <c r="I4" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -7970,28 +8018,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>686</v>
+      </c>
+      <c r="C5" t="s">
+        <v>685</v>
+      </c>
+      <c r="D5" t="s">
+        <v>729</v>
+      </c>
+      <c r="E5" t="s">
+        <v>731</v>
+      </c>
+      <c r="F5" t="s">
+        <v>687</v>
+      </c>
+      <c r="G5" t="s">
         <v>688</v>
       </c>
-      <c r="C5" t="s">
-        <v>687</v>
-      </c>
-      <c r="D5" t="s">
-        <v>731</v>
-      </c>
-      <c r="E5" t="s">
-        <v>733</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
+        <v>690</v>
+      </c>
+      <c r="I5" t="s">
         <v>689</v>
-      </c>
-      <c r="G5" t="s">
-        <v>690</v>
-      </c>
-      <c r="H5" t="s">
-        <v>692</v>
-      </c>
-      <c r="I5" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -8002,25 +8050,25 @@
         <v>296</v>
       </c>
       <c r="C6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="F6" t="s">
+        <v>733</v>
+      </c>
+      <c r="G6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H6" t="s">
+        <v>726</v>
+      </c>
+      <c r="I6" t="s">
         <v>734</v>
-      </c>
-      <c r="F6" t="s">
-        <v>735</v>
-      </c>
-      <c r="G6" t="s">
-        <v>583</v>
-      </c>
-      <c r="H6" t="s">
-        <v>728</v>
-      </c>
-      <c r="I6" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -8037,19 +8085,19 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
+        <v>762</v>
+      </c>
+      <c r="F7" t="s">
+        <v>763</v>
+      </c>
+      <c r="G7" t="s">
         <v>764</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>761</v>
+      </c>
+      <c r="I7" t="s">
         <v>765</v>
-      </c>
-      <c r="G7" t="s">
-        <v>766</v>
-      </c>
-      <c r="H7" t="s">
-        <v>763</v>
-      </c>
-      <c r="I7" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -8066,19 +8114,19 @@
         <v>106</v>
       </c>
       <c r="E8" t="s">
+        <v>766</v>
+      </c>
+      <c r="F8" t="s">
+        <v>767</v>
+      </c>
+      <c r="G8" t="s">
+        <v>811</v>
+      </c>
+      <c r="H8" t="s">
         <v>768</v>
       </c>
-      <c r="F8" t="s">
+      <c r="I8" t="s">
         <v>769</v>
-      </c>
-      <c r="G8" t="s">
-        <v>813</v>
-      </c>
-      <c r="H8" t="s">
-        <v>770</v>
-      </c>
-      <c r="I8" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -8092,22 +8140,22 @@
         <v>298</v>
       </c>
       <c r="D9" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E9" t="s">
+        <v>809</v>
+      </c>
+      <c r="F9" t="s">
+        <v>810</v>
+      </c>
+      <c r="G9" t="s">
         <v>811</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>812</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>813</v>
-      </c>
-      <c r="H9" t="s">
-        <v>814</v>
-      </c>
-      <c r="I9" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -8344,7 +8392,7 @@
         <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -8787,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>8</v>
@@ -8808,7 +8856,7 @@
         <v>9</v>
       </c>
       <c r="I18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -8837,7 +8885,7 @@
         <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -8845,7 +8893,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>8</v>
@@ -8866,7 +8914,7 @@
         <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -8874,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>8</v>
@@ -8895,7 +8943,7 @@
         <v>9</v>
       </c>
       <c r="I21" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -8903,7 +8951,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
@@ -8924,7 +8972,7 @@
         <v>9</v>
       </c>
       <c r="I22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -8935,7 +8983,7 @@
         <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D23" t="s">
         <v>343</v>
@@ -8953,7 +9001,7 @@
         <v>112</v>
       </c>
       <c r="I23" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -8961,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>23</v>
@@ -8982,7 +9030,7 @@
         <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -9011,7 +9059,7 @@
         <v>9</v>
       </c>
       <c r="I25" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -9019,7 +9067,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
@@ -9040,7 +9088,7 @@
         <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -9048,10 +9096,10 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D27" t="s">
         <v>343</v>
@@ -9069,7 +9117,7 @@
         <v>112</v>
       </c>
       <c r="I27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -9077,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>8</v>
@@ -9098,7 +9146,7 @@
         <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -9127,7 +9175,7 @@
         <v>112</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -9135,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>8</v>
@@ -9156,7 +9204,7 @@
         <v>9</v>
       </c>
       <c r="I30" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -9164,7 +9212,7 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>8</v>
@@ -9185,7 +9233,7 @@
         <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -9196,7 +9244,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D32" t="s">
         <v>106</v>
@@ -9214,7 +9262,7 @@
         <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
@@ -9407,7 +9455,7 @@
         <v>125</v>
       </c>
       <c r="H3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="I3" t="s">
         <v>366</v>
@@ -9456,22 +9504,22 @@
         <v>363</v>
       </c>
       <c r="D5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G5" t="s">
         <v>103</v>
       </c>
       <c r="I5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -9485,22 +9533,22 @@
         <v>363</v>
       </c>
       <c r="D6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="G6" t="s">
         <v>103</v>
       </c>
       <c r="I6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="J6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -9514,7 +9562,7 @@
         <v>363</v>
       </c>
       <c r="D7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -9526,10 +9574,10 @@
         <v>103</v>
       </c>
       <c r="I7" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="J7" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -9555,7 +9603,7 @@
         <v>103</v>
       </c>
       <c r="H8" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="I8" t="s">
         <v>145</v>
@@ -9575,10 +9623,10 @@
         <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E9" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F9" t="s">
         <v>392</v>
@@ -9587,10 +9635,10 @@
         <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J9" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -9604,10 +9652,10 @@
         <v>224</v>
       </c>
       <c r="D10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E10" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F10" t="s">
         <v>119</v>
@@ -9616,10 +9664,10 @@
         <v>103</v>
       </c>
       <c r="I10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="J10" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -9633,25 +9681,25 @@
         <v>224</v>
       </c>
       <c r="D11" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E11" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F11" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G11" t="s">
         <v>103</v>
       </c>
       <c r="H11" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="I11" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="J11" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -9665,10 +9713,10 @@
         <v>224</v>
       </c>
       <c r="D12" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E12" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F12" t="s">
         <v>119</v>
@@ -9677,13 +9725,13 @@
         <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="I12" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="J12" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -10036,13 +10084,13 @@
         <v>330</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -10059,13 +10107,13 @@
         <v>330</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>820</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -10073,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C16" s="12">
         <v>3</v>
@@ -10082,13 +10130,13 @@
         <v>331</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -10096,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C17" s="12">
         <v>5</v>
@@ -10105,7 +10153,7 @@
         <v>331</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -10113,7 +10161,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C18" s="12">
         <v>1</v>
@@ -10122,10 +10170,10 @@
         <v>202</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -10133,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
@@ -10142,10 +10190,10 @@
         <v>202</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -10214,10 +10262,10 @@
         <v>331</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -10234,13 +10282,13 @@
         <v>330</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -10257,13 +10305,13 @@
         <v>331</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -10280,16 +10328,16 @@
         <v>330</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -10306,16 +10354,16 @@
         <v>330</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -10441,16 +10489,16 @@
         <v>331</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>646</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -10458,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C33" s="12">
         <v>3</v>
@@ -10467,16 +10515,16 @@
         <v>331</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>636</v>
-      </c>
       <c r="G33" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -10484,7 +10532,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C34" s="12">
         <v>2</v>
@@ -10493,16 +10541,16 @@
         <v>331</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>642</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -10510,7 +10558,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C35" s="12">
         <v>4</v>
@@ -10519,16 +10567,16 @@
         <v>331</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>866</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -10536,7 +10584,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C36" s="12">
         <v>4</v>
@@ -10545,16 +10593,16 @@
         <v>330</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>866</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -10562,7 +10610,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C37" s="12">
         <v>10</v>
@@ -10582,7 +10630,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C38" s="12">
         <v>16</v>
@@ -10765,13 +10813,13 @@
         <v>331</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>410</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -10811,13 +10859,13 @@
         <v>331</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -10834,13 +10882,13 @@
         <v>331</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>678</v>
-      </c>
       <c r="H50" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -10848,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C51" s="12">
         <v>1</v>
@@ -10857,13 +10905,13 @@
         <v>331</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>705</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
@@ -10871,7 +10919,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C52" s="12">
         <v>1</v>
@@ -10880,16 +10928,16 @@
         <v>202</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -10897,25 +10945,25 @@
         <v>1</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="C53" s="12">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="C53" s="12">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -10992,7 +11040,7 @@
         <v>1</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C57" s="12">
         <v>5</v>
@@ -11001,10 +11049,10 @@
         <v>331</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -11042,23 +11090,40 @@
         <v>331</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>410</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C60" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="C60" s="12">
+        <v>4</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="b">
@@ -11399,22 +11464,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C4" t="s">
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E4" t="s">
         <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -11422,22 +11487,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C5" t="s">
         <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E5" t="s">
         <v>103</v>
       </c>
       <c r="F5" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G5" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -11534,7 +11599,7 @@
         <v>114</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>115</v>
@@ -11560,7 +11625,7 @@
         <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F2" t="s">
         <v>172</v>
@@ -11586,7 +11651,7 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F3" t="s">
         <v>120</v>
@@ -11609,16 +11674,16 @@
         <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G4" t="s">
+        <v>463</v>
+      </c>
+      <c r="H4" t="s">
         <v>464</v>
-      </c>
-      <c r="G4" t="s">
-        <v>465</v>
-      </c>
-      <c r="H4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -11629,22 +11694,22 @@
         <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D5" t="s">
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -11652,22 +11717,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F6" t="s">
         <v>172</v>
       </c>
       <c r="G6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -11675,22 +11740,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C7" t="s">
+        <v>623</v>
+      </c>
+      <c r="E7" t="s">
+        <v>627</v>
+      </c>
+      <c r="F7" t="s">
         <v>625</v>
       </c>
-      <c r="E7" t="s">
-        <v>629</v>
-      </c>
-      <c r="F7" t="s">
-        <v>627</v>
-      </c>
       <c r="G7" t="s">
+        <v>624</v>
+      </c>
+      <c r="H7" t="s">
         <v>626</v>
-      </c>
-      <c r="H7" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -11698,22 +11763,22 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>465</v>
+      </c>
+      <c r="C8" t="s">
+        <v>466</v>
+      </c>
+      <c r="E8" t="s">
+        <v>608</v>
+      </c>
+      <c r="F8" t="s">
         <v>467</v>
       </c>
-      <c r="C8" t="s">
+      <c r="G8" t="s">
         <v>468</v>
       </c>
-      <c r="E8" t="s">
-        <v>610</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>469</v>
-      </c>
-      <c r="G8" t="s">
-        <v>470</v>
-      </c>
-      <c r="H8" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -11721,22 +11786,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E9" t="s">
         <v>286</v>
       </c>
       <c r="F9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H9" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -11744,22 +11809,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C10" t="s">
+        <v>604</v>
+      </c>
+      <c r="E10" t="s">
+        <v>608</v>
+      </c>
+      <c r="F10" t="s">
+        <v>605</v>
+      </c>
+      <c r="G10" t="s">
         <v>606</v>
       </c>
-      <c r="E10" t="s">
-        <v>610</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>607</v>
-      </c>
-      <c r="G10" t="s">
-        <v>608</v>
-      </c>
-      <c r="H10" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -11767,22 +11832,22 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C11" t="s">
+        <v>620</v>
+      </c>
+      <c r="E11" t="s">
+        <v>608</v>
+      </c>
+      <c r="F11" t="s">
+        <v>605</v>
+      </c>
+      <c r="G11" t="s">
+        <v>621</v>
+      </c>
+      <c r="H11" t="s">
         <v>622</v>
-      </c>
-      <c r="E11" t="s">
-        <v>610</v>
-      </c>
-      <c r="F11" t="s">
-        <v>607</v>
-      </c>
-      <c r="G11" t="s">
-        <v>623</v>
-      </c>
-      <c r="H11" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11790,22 +11855,22 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C12" t="s">
+        <v>755</v>
+      </c>
+      <c r="E12" t="s">
+        <v>756</v>
+      </c>
+      <c r="F12" t="s">
         <v>757</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>758</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>759</v>
-      </c>
-      <c r="G12" t="s">
-        <v>760</v>
-      </c>
-      <c r="H12" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -11813,22 +11878,22 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C13" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E13" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="F13" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G13" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="H13" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -11836,22 +11901,22 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C14" t="s">
+        <v>893</v>
+      </c>
+      <c r="E14" t="s">
+        <v>894</v>
+      </c>
+      <c r="F14" t="s">
+        <v>844</v>
+      </c>
+      <c r="G14" t="s">
         <v>895</v>
       </c>
-      <c r="E14" t="s">
+      <c r="H14" t="s">
         <v>896</v>
-      </c>
-      <c r="F14" t="s">
-        <v>846</v>
-      </c>
-      <c r="G14" t="s">
-        <v>897</v>
-      </c>
-      <c r="H14" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -11927,16 +11992,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E2" t="s">
         <v>630</v>
-      </c>
-      <c r="C2" t="s">
-        <v>639</v>
-      </c>
-      <c r="D2" t="s">
-        <v>631</v>
-      </c>
-      <c r="E2" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -11944,16 +12009,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D3" t="s">
         <v>638</v>
       </c>
-      <c r="D3" t="s">
-        <v>640</v>
-      </c>
       <c r="E3" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -11978,13 +12043,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>601</v>
+      </c>
+      <c r="D5" t="s">
         <v>603</v>
       </c>
-      <c r="D5" t="s">
-        <v>605</v>
-      </c>
       <c r="E5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -11992,16 +12057,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" t="s">
         <v>507</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>508</v>
-      </c>
-      <c r="D6" t="s">
-        <v>509</v>
-      </c>
-      <c r="E6" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -12009,16 +12074,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>664</v>
+      </c>
+      <c r="C7" t="s">
+        <v>667</v>
+      </c>
+      <c r="D7" t="s">
+        <v>665</v>
+      </c>
+      <c r="E7" t="s">
         <v>666</v>
-      </c>
-      <c r="C7" t="s">
-        <v>669</v>
-      </c>
-      <c r="D7" t="s">
-        <v>667</v>
-      </c>
-      <c r="E7" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -12040,16 +12105,16 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>698</v>
+      </c>
+      <c r="C9" t="s">
+        <v>699</v>
+      </c>
+      <c r="D9" t="s">
         <v>700</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>701</v>
-      </c>
-      <c r="D9" t="s">
-        <v>702</v>
-      </c>
-      <c r="E9" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -12057,13 +12122,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D10" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E10" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -12085,16 +12150,16 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
+        <v>553</v>
+      </c>
+      <c r="C12" t="s">
+        <v>554</v>
+      </c>
+      <c r="D12" t="s">
         <v>555</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>556</v>
-      </c>
-      <c r="D12" t="s">
-        <v>557</v>
-      </c>
-      <c r="E12" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -12102,16 +12167,16 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
+        <v>670</v>
+      </c>
+      <c r="C13" t="s">
+        <v>671</v>
+      </c>
+      <c r="D13" t="s">
         <v>672</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>673</v>
-      </c>
-      <c r="D13" t="s">
-        <v>674</v>
-      </c>
-      <c r="E13" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -12119,16 +12184,16 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C14" t="s">
+        <v>680</v>
+      </c>
+      <c r="D14" t="s">
+        <v>681</v>
+      </c>
+      <c r="E14" t="s">
         <v>682</v>
-      </c>
-      <c r="D14" t="s">
-        <v>683</v>
-      </c>
-      <c r="E14" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -12136,16 +12201,16 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
+        <v>710</v>
+      </c>
+      <c r="C15" t="s">
+        <v>711</v>
+      </c>
+      <c r="D15" t="s">
         <v>712</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>713</v>
-      </c>
-      <c r="D15" t="s">
-        <v>714</v>
-      </c>
-      <c r="E15" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -12153,16 +12218,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
+        <v>716</v>
+      </c>
+      <c r="C16" t="s">
+        <v>717</v>
+      </c>
+      <c r="D16" t="s">
         <v>718</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>719</v>
-      </c>
-      <c r="D16" t="s">
-        <v>720</v>
-      </c>
-      <c r="E16" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -12170,13 +12235,13 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
+        <v>550</v>
+      </c>
+      <c r="D17" t="s">
+        <v>551</v>
+      </c>
+      <c r="E17" t="s">
         <v>552</v>
-      </c>
-      <c r="D17" t="s">
-        <v>553</v>
-      </c>
-      <c r="E17" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -12184,16 +12249,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
+        <v>735</v>
+      </c>
+      <c r="C18" t="s">
         <v>737</v>
       </c>
-      <c r="C18" t="s">
-        <v>739</v>
-      </c>
       <c r="D18" t="s">
+        <v>736</v>
+      </c>
+      <c r="E18" t="s">
         <v>738</v>
-      </c>
-      <c r="E18" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -12235,16 +12300,16 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
+        <v>694</v>
+      </c>
+      <c r="C21" t="s">
+        <v>695</v>
+      </c>
+      <c r="D21" t="s">
+        <v>697</v>
+      </c>
+      <c r="E21" t="s">
         <v>696</v>
-      </c>
-      <c r="C21" t="s">
-        <v>697</v>
-      </c>
-      <c r="D21" t="s">
-        <v>699</v>
-      </c>
-      <c r="E21" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -12252,13 +12317,13 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
+        <v>470</v>
+      </c>
+      <c r="D22" t="s">
+        <v>471</v>
+      </c>
+      <c r="E22" t="s">
         <v>472</v>
-      </c>
-      <c r="D22" t="s">
-        <v>473</v>
-      </c>
-      <c r="E22" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -12269,7 +12334,7 @@
         <v>210</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D23" t="s">
         <v>90</v>
@@ -12286,7 +12351,7 @@
         <v>336</v>
       </c>
       <c r="C24" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D24" t="s">
         <v>337</v>
@@ -12303,13 +12368,13 @@
         <v>336</v>
       </c>
       <c r="C25" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D25" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E25" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -12317,16 +12382,16 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C26" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D26" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E26" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -12368,13 +12433,13 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D29" t="s">
+        <v>739</v>
+      </c>
+      <c r="E29" t="s">
         <v>741</v>
-      </c>
-      <c r="E29" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -12382,16 +12447,16 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C30" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D30" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E30" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -12399,16 +12464,16 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C31" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D31" t="s">
+        <v>745</v>
+      </c>
+      <c r="E31" t="s">
         <v>747</v>
-      </c>
-      <c r="E31" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -12416,16 +12481,16 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C32" t="s">
         <v>218</v>
       </c>
       <c r="D32" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E32" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -12433,16 +12498,16 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C33" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D33" t="s">
+        <v>752</v>
+      </c>
+      <c r="E33" t="s">
         <v>754</v>
-      </c>
-      <c r="E33" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -12450,13 +12515,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
+        <v>890</v>
+      </c>
+      <c r="D34" t="s">
+        <v>891</v>
+      </c>
+      <c r="E34" t="s">
         <v>892</v>
-      </c>
-      <c r="D34" t="s">
-        <v>893</v>
-      </c>
-      <c r="E34" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -12464,21 +12529,33 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
+        <v>903</v>
+      </c>
+      <c r="C35" t="s">
+        <v>904</v>
+      </c>
+      <c r="D35" t="s">
+        <v>902</v>
+      </c>
+      <c r="E35" t="s">
         <v>905</v>
-      </c>
-      <c r="C35" t="s">
-        <v>906</v>
-      </c>
-      <c r="D35" t="s">
-        <v>904</v>
-      </c>
-      <c r="E35" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>698</v>
+      </c>
+      <c r="C36" t="s">
+        <v>929</v>
+      </c>
+      <c r="D36" t="s">
+        <v>930</v>
+      </c>
+      <c r="E36" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -12579,7 +12656,7 @@
         <v>197</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>246</v>
@@ -12704,16 +12781,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>815</v>
+      </c>
+      <c r="C8" t="s">
+        <v>816</v>
+      </c>
+      <c r="D8" t="s">
         <v>817</v>
       </c>
-      <c r="C8" t="s">
-        <v>818</v>
-      </c>
-      <c r="D8" t="s">
-        <v>819</v>
-      </c>
       <c r="F8" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12721,13 +12798,13 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C9" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D9" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12735,16 +12812,16 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>828</v>
+      </c>
+      <c r="C10" t="s">
+        <v>829</v>
+      </c>
+      <c r="D10" t="s">
+        <v>831</v>
+      </c>
+      <c r="E10" t="s">
         <v>830</v>
-      </c>
-      <c r="C10" t="s">
-        <v>831</v>
-      </c>
-      <c r="D10" t="s">
-        <v>833</v>
-      </c>
-      <c r="E10" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12752,19 +12829,19 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
+        <v>887</v>
+      </c>
+      <c r="C11" t="s">
+        <v>885</v>
+      </c>
+      <c r="D11" t="s">
+        <v>888</v>
+      </c>
+      <c r="E11" t="s">
+        <v>885</v>
+      </c>
+      <c r="F11" t="s">
         <v>889</v>
-      </c>
-      <c r="C11" t="s">
-        <v>887</v>
-      </c>
-      <c r="D11" t="s">
-        <v>890</v>
-      </c>
-      <c r="E11" t="s">
-        <v>887</v>
-      </c>
-      <c r="F11" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12772,13 +12849,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C12" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D12" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E12" t="s">
         <v>202</v>

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410A7766-C58E-40F3-BAEC-3D422FA03C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ECC767-F08E-4E61-8937-85AAD5E8F846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="5" activeTab="5" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome!" sheetId="15" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="936">
   <si>
     <t>Capacitance</t>
   </si>
@@ -2855,6 +2855,18 @@
   </si>
   <si>
     <t>Buffer, Non-Inverting 1 Element 1 Bit per Element 3-State Output SC-70-5</t>
+  </si>
+  <si>
+    <t>M4 Bolt</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/92095A478/</t>
+  </si>
+  <si>
+    <t>18mm</t>
+  </si>
+  <si>
+    <t>18-8 Stainless Steel Button Head Hex-Drive Screw</t>
   </si>
 </sst>
 </file>
@@ -3189,6 +3201,23 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -3276,20 +3305,6 @@
       </extLst>
     </dxf>
     <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3339,9 +3354,6 @@
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <extLst>
@@ -3401,13 +3413,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
   <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="76"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="75"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="73"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3419,11 +3431,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:I20" totalsRowShown="0">
   <autoFilter ref="A1:I20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="78"/>
-    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="41"/>
     <tableColumn id="1" xr3:uid="{727DF6C0-6BC9-4CBC-ACBD-F7D7801F3DED}" name="Color"/>
     <tableColumn id="6" xr3:uid="{2F89F121-2031-4E76-8B64-C6BE1AC4E5A7}" name="Mount Type"/>
-    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="40"/>
     <tableColumn id="3" xr3:uid="{95A3DF17-FA71-419C-9869-87ACAC774187}" name="Dome"/>
     <tableColumn id="9" xr3:uid="{51A8C34B-CA0A-4A26-89E6-8BD3AFCDABB1}" name="Millicandela"/>
     <tableColumn id="4" xr3:uid="{30ACC022-FAF3-44FA-97E2-DA5C989B54D7}" name="Part Number"/>
@@ -3603,20 +3615,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="72">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="70"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="66"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="65"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3639,13 +3651,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="63">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="62"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3665,8 +3677,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="77"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3676,11 +3688,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="61">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="59"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -3691,25 +3703,25 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="58">
   <autoFilter ref="A1:E11" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="52">
   <autoFilter ref="A1:I10" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="50"/>
     <tableColumn id="4" xr3:uid="{D6AD8AA5-BC88-4F36-A647-B68EB5308316}" name="Automotive Fuse Size"/>
     <tableColumn id="1" xr3:uid="{5D9981C8-F221-4013-A9BA-4E5BF3474E5D}" name="Trip Current"/>
     <tableColumn id="2" xr3:uid="{494ED5E9-E1DA-4E76-9EAF-806837FCC14C}" name="Package"/>
@@ -3723,15 +3735,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="49">
   <autoFilter ref="A1:F11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="6">
-    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="45"/>
-    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11127,9 +11139,23 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C61" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="C61" s="12">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="b">

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ECC767-F08E-4E61-8937-85AAD5E8F846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D1F634-4F8D-47BB-9302-9316513CDA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="939">
   <si>
     <t>Capacitance</t>
   </si>
@@ -2866,7 +2866,16 @@
     <t>18mm</t>
   </si>
   <si>
-    <t>18-8 Stainless Steel Button Head Hex-Drive Screw</t>
+    <t>https://www.mcmaster.com/92095A194/</t>
+  </si>
+  <si>
+    <t>16mm</t>
+  </si>
+  <si>
+    <t>M4 x 0.7 mm Thread Size, 16 mm Long</t>
+  </si>
+  <si>
+    <t>M4 x 0.7 mm Thread Size, 18 mm Long</t>
   </si>
 </sst>
 </file>
@@ -3305,7 +3314,37 @@
       </extLst>
     </dxf>
     <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3338,36 +3377,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3413,13 +3422,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
   <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="69"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="68"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="66"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3615,20 +3624,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="78">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="71"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="67"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="66"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="77"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="73"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="72"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3651,13 +3660,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="65">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="64"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3677,8 +3686,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="62"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -11154,14 +11163,28 @@
         <v>934</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C62" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="C62" s="12">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="b">

--- a/Altium Parts.xlsx
+++ b/Altium Parts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MIL-Altium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D1F634-4F8D-47BB-9302-9316513CDA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD16EA0-038B-4E80-9EE3-E86BFFF512BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{78817FF2-1CC3-4A74-8C91-2AFFF0842C3F}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="949">
   <si>
     <t>Capacitance</t>
   </si>
@@ -2876,6 +2876,36 @@
   </si>
   <si>
     <t>M4 x 0.7 mm Thread Size, 18 mm Long</t>
+  </si>
+  <si>
+    <t>2.7k</t>
+  </si>
+  <si>
+    <t>AC0603FR-072K7L</t>
+  </si>
+  <si>
+    <t>2.7 kOhms ±1% 0.1W, 1/10W Chip Resistor 0603 (1608 Metric) Automotive AEC-Q200, Moisture Resistant Thick Film</t>
+  </si>
+  <si>
+    <t>USB 2.0, 7-port</t>
+  </si>
+  <si>
+    <t>TUSB2077APTRG4</t>
+  </si>
+  <si>
+    <t>USB Hub Controller USB 2.0 USB Interface 48-LQFP (7x7)</t>
+  </si>
+  <si>
+    <t>USB-A Triple</t>
+  </si>
+  <si>
+    <t>Femake</t>
+  </si>
+  <si>
+    <t>1002-012-01020</t>
+  </si>
+  <si>
+    <t>USB-A (USB TYPE-A), Stacked USB 2.0 Receptacle Connector 12 Position Through Hole, Right Angle</t>
   </si>
 </sst>
 </file>
@@ -3058,57 +3088,6 @@
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3340,22 +3319,6 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -3377,6 +3340,73 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3422,13 +3452,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}" name="Capacitors" displayName="Capacitors" ref="A1:I49" totalsRowShown="0">
   <autoFilter ref="A1:I49" xr:uid="{66640DDE-A600-4D40-886A-D93F6DB5FAB3}"/>
   <tableColumns count="9">
-    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{B97E7FE0-D68A-4659-9DE5-965B7C74FB58}" name="Added to Altium?" dataDxfId="68"/>
     <tableColumn id="1" xr3:uid="{BDC3005D-8889-49B9-B05B-9B4FB822D92C}" name="Capacitance"/>
-    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{204119AE-0485-4922-A3C8-7CDD048C63F5}" name="Package" dataDxfId="67"/>
     <tableColumn id="3" xr3:uid="{13A5BE24-7E3B-42A7-BB30-CF0EA6F4873D}" name="Max Voltage"/>
     <tableColumn id="4" xr3:uid="{D4BF488D-A80E-4525-A0D1-501D554CEDF7}" name="Tolerance"/>
-    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{08BCE889-36CA-4A02-9976-7D80BAE9681D}" name="Mounting Type" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{B82114B5-A4D9-4327-9F80-0D9587A64062}" name="Polarity" dataDxfId="65"/>
     <tableColumn id="6" xr3:uid="{31CBAF16-36EA-4251-9AC8-58F6F46900E9}" name="Material"/>
     <tableColumn id="7" xr3:uid="{571D64FC-0F67-4FD0-B071-89D71A56F7C6}" name="Manufacturer Part Number"/>
   </tableColumns>
@@ -3440,11 +3470,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}" name="LEDs" displayName="LEDs" ref="A1:I20" totalsRowShown="0">
   <autoFilter ref="A1:I20" xr:uid="{C732A860-4A42-46A7-A5FA-C00091FE4BA3}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{B2E48D06-BAB0-4133-877E-867AB2EC32E9}" name="Added to Altium?" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{22D7B7BF-E3CF-4637-92B5-B74434B0A877}" name="Type" dataDxfId="31"/>
     <tableColumn id="1" xr3:uid="{727DF6C0-6BC9-4CBC-ACBD-F7D7801F3DED}" name="Color"/>
     <tableColumn id="6" xr3:uid="{2F89F121-2031-4E76-8B64-C6BE1AC4E5A7}" name="Mount Type"/>
-    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{59EEDA5E-A95B-4620-BC5E-79C5C5FB8AFC}" name="Package" dataDxfId="30"/>
     <tableColumn id="3" xr3:uid="{95A3DF17-FA71-419C-9869-87ACAC774187}" name="Dome"/>
     <tableColumn id="9" xr3:uid="{51A8C34B-CA0A-4A26-89E6-8BD3AFCDABB1}" name="Millicandela"/>
     <tableColumn id="4" xr3:uid="{30ACC022-FAF3-44FA-97E2-DA5C989B54D7}" name="Part Number"/>
@@ -3455,10 +3485,10 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}" name="ICs_10" displayName="ICs_10" ref="A1:G10" totalsRowShown="0" headerRowDxfId="29">
   <autoFilter ref="A1:G10" xr:uid="{EF03BBEA-AE4C-45BB-9CD5-736F7FCCE237}"/>
   <tableColumns count="7">
-    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{2AE73037-16FE-4A0E-B4B4-CF3863388825}" name="Added to Altium?" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{D4673AC2-9436-437D-9DE0-521034F11263}" name="Memory Organization"/>
     <tableColumn id="6" xr3:uid="{088605FE-5C4A-4A9F-9607-7699E9A0ED47}" name="Total Capacity"/>
     <tableColumn id="7" xr3:uid="{E9CAAB16-100E-4178-A533-7FCE76F08C9F}" name="Interface"/>
@@ -3477,7 +3507,7 @@
     <sortCondition ref="B1:B13"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{6C04560D-813B-4E79-B81B-87E653E3F958}" name="Added to Altium?" dataDxfId="27"/>
     <tableColumn id="1" xr3:uid="{07652CF2-D7CA-452D-A87D-CEBA35FEC12A}" name="Function"/>
     <tableColumn id="2" xr3:uid="{A9FCB299-A552-4123-B45A-F31F0DC5BB9B}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{2F50D30B-F60A-4BAF-AE6D-0A3909047904}" name="Description"/>
@@ -3487,54 +3517,54 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{A40CA8A6-1C4E-486A-ACF3-77702798EDC5}" name="Mounts_Pads_Vias" displayName="Mounts_Pads_Vias" ref="A1:H11" totalsRowShown="0" headerRowDxfId="26">
   <autoFilter ref="A1:H11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="8">
-    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="34"/>
-    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{AEAC8F87-1C2D-4AB2-AF57-3B985B9984E8}" name="Added to Altium?" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{013363CF-8CB8-438A-8840-8BE5C88DD21A}" name="Type" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{D05BE736-0061-4B08-B525-77CB6D52275D}" name="Name" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{7A597B79-DB0B-4F42-A26A-5BFC2BE446DB}" name="Shape" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{9BE909D1-CB3E-47D8-89BD-A5A9007FC19A}" name="Hole Size (diameter)" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{9D59173A-B663-440B-ABB2-B4420C0F2F76}" name="Copper X-Size" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{0B466DAF-712F-4EDB-BA0B-281F181D75D1}" name="Copper Y-Size" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{63AE9014-61F7-479D-A241-EAA26D52AAA0}" name="Description" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}" name="MCUs" displayName="MCUs" ref="A1:J11" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}" name="MCUs" displayName="MCUs" ref="A1:J11" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:J11" xr:uid="{9DA4F768-7F47-4563-8367-8C9704917FC2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J11">
     <sortCondition ref="B1:B11"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="7" xr3:uid="{B7904B75-EB47-4AE0-AC16-835BCD406E73}" name="Added to Altium?" dataDxfId="25"/>
-    <tableColumn id="1" xr3:uid="{0881C807-AE0D-4E97-942D-F1BB4BC72740}" name="Name" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{FF11C1E0-268B-4AB9-A529-8334EF2C69FD}" name="# GPIO" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{55162BE7-C291-4B9F-ABE8-A7DE102A5A2F}" name="UART" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{12871EC5-67F1-442C-B9F6-E715FA2B13DA}" name="SPI" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{0676FDA2-81C4-49A9-A3D1-DEE7F28D8014}" name="I2C" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{4D86DECE-60FC-46A0-B57F-AB144D9C1459}" name="PWM" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{F498CA82-C855-4B59-BFFB-E076763E2C7B}" name="USB" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{1C8B55E3-7B48-484B-9DEC-D60D33855BF8}" name="Part Number" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{EB01044E-239A-43EB-B0C2-1F87DDB54160}" name="Description" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{B7904B75-EB47-4AE0-AC16-835BCD406E73}" name="Added to Altium?" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{0881C807-AE0D-4E97-942D-F1BB4BC72740}" name="Name" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{FF11C1E0-268B-4AB9-A529-8334EF2C69FD}" name="# GPIO" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{55162BE7-C291-4B9F-ABE8-A7DE102A5A2F}" name="UART" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{12871EC5-67F1-442C-B9F6-E715FA2B13DA}" name="SPI" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{0676FDA2-81C4-49A9-A3D1-DEE7F28D8014}" name="I2C" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{4D86DECE-60FC-46A0-B57F-AB144D9C1459}" name="PWM" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{F498CA82-C855-4B59-BFFB-E076763E2C7B}" name="USB" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{1C8B55E3-7B48-484B-9DEC-D60D33855BF8}" name="Part Number" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{EB01044E-239A-43EB-B0C2-1F87DDB54160}" name="Description" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}" name="Resistors" displayName="Resistors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}" name="Resistors" displayName="Resistors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77">
   <autoFilter ref="A1:H100" xr:uid="{FE99B236-7512-4792-AE6E-EED4D7BDA003}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H50">
     <sortCondition ref="C1:C50"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{5CCC4BAB-E9A7-42D2-BFCF-40A14E4FCFB3}" name="Added to Altium?" dataDxfId="13"/>
-    <tableColumn id="1" xr3:uid="{E2BB1AD3-36C9-4D80-8A78-E46D0D28B43D}" name="Resistance" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{C2F2285A-BFA3-4714-8945-6FE63C9CDE81}" name="Res (Raw)" dataDxfId="11">
+    <tableColumn id="8" xr3:uid="{5CCC4BAB-E9A7-42D2-BFCF-40A14E4FCFB3}" name="Added to Altium?" dataDxfId="76"/>
+    <tableColumn id="1" xr3:uid="{E2BB1AD3-36C9-4D80-8A78-E46D0D28B43D}" name="Resistance" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{C2F2285A-BFA3-4714-8945-6FE63C9CDE81}" name="Res (Raw)" dataDxfId="74">
       <calculatedColumnFormula>IF(ISNUMBER(B2),
 IF(B2=0,"",B2),
 VALUE(LEFT(B2,LEN(B2)-1))*
@@ -3542,11 +3572,11 @@
 IF(RIGHT(B2,1)="M",1000000,
 IF(RIGHT(B2,1)="m",0.001,1))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{67EED117-D01D-4FE8-BB40-D7D8F55BAB48}" name="Tolerance" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{F1269AFE-5CA5-4F00-93B8-6023E945504D}" name="Package" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{A4374340-1758-433F-80B6-83ABF6D97E11}" name="Wattage" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{7C53E4E9-C23D-4482-9A46-441AB8A4E1B1}" name="Part Number" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{BD8216A4-1B75-4738-A589-0D33231AD075}" name="Description" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{67EED117-D01D-4FE8-BB40-D7D8F55BAB48}" name="Tolerance" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{F1269AFE-5CA5-4F00-93B8-6023E945504D}" name="Package" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{A4374340-1758-433F-80B6-83ABF6D97E11}" name="Wattage" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{7C53E4E9-C23D-4482-9A46-441AB8A4E1B1}" name="Part Number" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{BD8216A4-1B75-4738-A589-0D33231AD075}" name="Description" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3624,20 +3654,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}" name="Connectors" displayName="Connectors" ref="A1:H100" totalsRowShown="0" headerRowDxfId="64">
   <autoFilter ref="A1:H100" xr:uid="{7090E628-1F8E-4CB3-BC5C-768E76CEFDDC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
     <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="77"/>
-    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="71"/>
-    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{CE9E315A-1702-4F78-8ECF-1DA1A2B792AA}" name="Added to Altium?" dataDxfId="63"/>
+    <tableColumn id="1" xr3:uid="{D5AE5A29-FEF0-4556-97F0-002479587894}" name="Series / Family" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{8673F73F-EA18-4F48-837C-C3D933082CD8}" name="# Pins" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{F61E1994-58CD-4ECF-A835-1786BECF70C2}" name="Gender (plug/port)" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{ADD992CB-74CD-4839-9C1F-4CA1C98DDDE6}" name="Part Number" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{0052054B-61D9-4444-933B-4830DE18EF5D}" name="Mating Connector Part Number" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{DF57140F-10E9-43CB-BE16-5AB59D2592F7}" name="Notes" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{E04857DF-CEB1-4D64-87C3-2580C252E44F}" name="Description" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3660,13 +3690,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}" name="Diodes" displayName="Diodes" ref="A1:H20" totalsRowShown="0" headerRowDxfId="55">
   <autoFilter ref="A1:H20" xr:uid="{AC1B69C7-59BA-492E-BEF3-378F8F5A5F42}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
     <sortCondition ref="B1:B20"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{373BF80E-AE0E-45C8-9A43-A9D96680B6E9}" name="Added to Altium?" dataDxfId="54"/>
     <tableColumn id="1" xr3:uid="{3176E398-8316-4079-97C6-E10CED1CC775}" name="Type"/>
     <tableColumn id="2" xr3:uid="{DFDAC67A-8333-4623-A218-F2BB6C8E25E6}" name="Breakdown voltage"/>
     <tableColumn id="3" xr3:uid="{3A72F6DE-D147-42DD-9C1C-BA3A3545DE11}" name="Max Forward Current"/>
@@ -3686,8 +3716,8 @@
     <sortCondition ref="B1:B50"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{2DF829CD-290D-41D3-B284-4B22DE33C4AA}" name="Added to Altium?" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{0460994E-DB61-407B-B7D3-3CAA8ED4BC9D}" name="Function" dataDxfId="52"/>
     <tableColumn id="6" xr3:uid="{F86F95F1-F9FE-4146-B379-63E1029BD91F}" name="Notes"/>
     <tableColumn id="1" xr3:uid="{B62DE98C-40C5-4F02-871A-56E6F423B932}" name="Part Number"/>
     <tableColumn id="3" xr3:uid="{613F07FA-6CA3-413B-A8EC-C111F4721AB4}" name="Description"/>
@@ -3697,11 +3727,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}" name="Devices" displayName="Devices" ref="A1:F50" totalsRowShown="0" headerRowDxfId="51">
   <autoFilter ref="A1:F50" xr:uid="{C5737D88-F4D8-4117-9BA5-1B2CC31DE11A}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{6415E46E-CEE3-460F-B779-529E15CD07B6}" name="Added to Altium?" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{A1AE6712-2A25-444F-8418-5CCFC5CDB835}" name="Series / Purpose" dataDxfId="49"/>
     <tableColumn id="9" xr3:uid="{6F530F3C-B40B-43DA-AB86-21341EB4DAD1}" name="Device"/>
     <tableColumn id="1" xr3:uid="{4AA09E23-76BE-4EAC-BAB7-D19DB7FEF15D}" name="Type"/>
     <tableColumn id="5" xr3:uid="{79DDF2A7-4DA6-48DB-8655-801CD7025B51}" name="Part Number"/>
@@ -3712,25 +3742,25 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" headerRowDxfId="48">
   <autoFilter ref="A1:E11" xr:uid="{EE7552C4-F486-457F-A2F8-480493B7351C}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="57"/>
-    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{7A1ACCA6-7C12-421C-A8B0-DAF52C5B82F1}" name="Added to Altium?" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{29766E43-A003-4F30-8FBC-98197408FA6D}" name="Part Number" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{9E0E83BD-C619-4B71-B8D8-093D6B07D9D5}" name="Package" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{6C643D04-D582-419C-9C7F-1B57D4315CFE}" name="Resistance" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{67D14711-9F21-4BBC-9182-15BB5F898016}" name="Description" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}" name="Fuses" displayName="Fuses" ref="A1:I10" totalsRowShown="0" headerRowDxfId="42">
   <autoFilter ref="A1:I10" xr:uid="{53E52592-BBF3-4884-BA3C-21683DC4F0F1}"/>
   <tableColumns count="9">
-    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{9030A4FE-0A13-4A65-8271-CB2306DED874}" name="Added to Altium?" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{7A093B6F-93A8-4A04-9A40-8451BE8854E4}" name="Type" dataDxfId="40"/>
     <tableColumn id="4" xr3:uid="{D6AD8AA5-BC88-4F36-A647-B68EB5308316}" name="Automotive Fuse Size"/>
     <tableColumn id="1" xr3:uid="{5D9981C8-F221-4013-A9BA-4E5BF3474E5D}" name="Trip Current"/>
     <tableColumn id="2" xr3:uid="{494ED5E9-E1DA-4E76-9EAF-806837FCC14C}" name="Package"/>
@@ -3744,15 +3774,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}" name="Inductors" displayName="Inductors" ref="A1:F11" totalsRowShown="0" headerRowDxfId="39">
   <autoFilter ref="A1:F11" xr:uid="{8788865D-3714-4394-BD76-99FF24EF6888}"/>
   <tableColumns count="6">
-    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="48"/>
-    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{67CA846A-F07D-4034-8F63-B4E47CA7F931}" name="Added to Altium?" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{EBC427FC-C649-421F-A511-F4C6E090217A}" name="Inductance" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{B8135C27-240F-4D83-9F04-23BE8CE5150A}" name="Max Current" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{57FAF0ED-182E-4A05-89A5-EE5FE9CF2C31}" name="Package" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{5B4ACDCC-FB26-4063-91C8-D6D43ABD7134}" name="Part Number" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{CFE06357-AAEA-49E4-8ED8-14478316C7C8}" name="Description" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6708,20 +6738,30 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="B50" s="15">
-        <v>0</v>
-      </c>
-      <c r="C50" s="17" t="str">
+        <v>1</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>939</v>
+      </c>
+      <c r="C50" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
+        <v>2700</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>940</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>941</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="18" t="b">
@@ -11188,9 +11228,23 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C63" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C63" s="12">
+        <v>12</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="b">
@@ -12609,7 +12663,19 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>314</v>
+      </c>
+      <c r="C37" t="s">
+        <v>942</v>
+      </c>
+      <c r="D37" t="s">
+        <v>943</v>
+      </c>
+      <c r="E37" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
